--- a/data/sxbet/ligas/Premier League/trades.xlsx
+++ b/data/sxbet/ligas/Premier League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,110 +531,318 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>0x82023bc913cac320bbcec8856b93c61ced3824bae2ff614f7aeb447196f63721</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>139.07045</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.7913</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1785492025</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>175.760442</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0xb79b0374865c7617b60514b2180feb26aead2aaca0895843000b71787d8212f5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>38.81386</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.7913</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1785492024</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>49.053852</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>0x35c722e47edc576e91fff2a56006e70c47630baaf10fd0a9c8c7187b33e14e24</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.3113</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Premier League</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny vs Spartak Moskva</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Spartak Moskva</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0xba2ac566f21d9b66fba41da0a24a5d93737f4a0c2789de13002227a82662899c</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>L19537277</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>1785344429</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1785691800</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>3.212851</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premier League/trades.xlsx
+++ b/data/sxbet/ligas/Premier League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x82023bc913cac320bbcec8856b93c61ced3824bae2ff614f7aeb447196f63721</t>
+          <t>0xa0c8d19ccd8222fe5808f3173eb4463c8de341ddcfcb086f400632089e4f0be4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,15 +539,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>139.07045</t>
+          <t>50.36</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7913</t>
+          <t>1.3375</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785492025</t>
+          <t>1785497556</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>175.760442</t>
+          <t>149.214815</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xb79b0374865c7617b60514b2180feb26aead2aaca0895843000b71787d8212f5</t>
+          <t>0x284f0b4a1de283358a3577badffac14ecc5afcfdc28ce21985a9cb86481ba6cc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x6d158A0b6c9Df0483460f6a656673630210CAA4a</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>38.81386</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7913</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -667,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Rodina Moskva vs Rostov FK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Rostov FK</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+          <t>0xc2ed80c842ab0c1d24361f465ff9c0b8137d5178739873b6e3325008d77dd204</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536024</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785492024</t>
+          <t>1785497412</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>49.053852</t>
+          <t>224.089636</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,110 +755,318 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>0x82023bc913cac320bbcec8856b93c61ced3824bae2ff614f7aeb447196f63721</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>139.07045</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.7913</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1785492025</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>175.760442</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0xb79b0374865c7617b60514b2180feb26aead2aaca0895843000b71787d8212f5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>38.81386</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.7913</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1785492024</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>49.053852</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>0x35c722e47edc576e91fff2a56006e70c47630baaf10fd0a9c8c7187b33e14e24</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.3113</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Premier League</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny vs Spartak Moskva</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Spartak Moskva</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0xba2ac566f21d9b66fba41da0a24a5d93737f4a0c2789de13002227a82662899c</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>L19537277</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1785344429</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1785691800</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>3.212851</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premier League/trades.xlsx
+++ b/data/sxbet/ligas/Premier League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xa0c8d19ccd8222fe5808f3173eb4463c8de341ddcfcb086f400632089e4f0be4</t>
+          <t>0x1638d462ac081048e75f74389a4ff26e18b1ae1b526d3aeb9de1440589cd1e5d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50.36</t>
+          <t>242.37998</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3375</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785497556</t>
+          <t>1785522300</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>149.214815</t>
+          <t>336.638861</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x284f0b4a1de283358a3577badffac14ecc5afcfdc28ce21985a9cb86481ba6cc</t>
+          <t>0xbb7e9ff01a18bfc8edad554bb31f15afc9af81a591df798303c216a31f4f60a2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x6d158A0b6c9Df0483460f6a656673630210CAA4a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>42.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.3912</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Rodina Moskva vs Rostov FK</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Rostov FK</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xc2ed80c842ab0c1d24361f465ff9c0b8137d5178739873b6e3325008d77dd204</t>
+          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19536024</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785497412</t>
+          <t>1785519268</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>224.089636</t>
+          <t>109.571885</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,23 +755,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x82023bc913cac320bbcec8856b93c61ced3824bae2ff614f7aeb447196f63721</t>
+          <t>0xb20c524d4e546a7083e83d50954cb82e74d2f35919a693305ef85bcd1297f018</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>139.07045</t>
+          <t>6.81967</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7913</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785492025</t>
+          <t>1785519268</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>175.760442</t>
+          <t>9.99219</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,28 +859,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xb79b0374865c7617b60514b2180feb26aead2aaca0895843000b71787d8212f5</t>
+          <t>0x4f0a3bc80edb843b0944d88bf4e31147f77d117de6bec90e861ee3f30e05ab04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38.81386</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7913</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -891,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785492024</t>
+          <t>1785519266</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>49.053852</t>
+          <t>25.18451</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,110 +963,854 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>0x5ba31b6e54e59ca06de6605e21a3984e6bef3be97c4a38cb1fef0f420c3c5762</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.5488</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1785517580</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>9.111617</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0x34ae51184c54f771408cd03c9262de0e4ea1554f41b9cf4d3f7f2c5d4d746850</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>13.93611</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.5488</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1785517575</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>25.3961</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0x7029f30f1995c9929d909d63df9f8e25356451c2543674cd96d9a354775d1cd1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.7113</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Rodina Moskva vs Rostov FK</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Rodina Moskva</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Rostov FK</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x79bda80ec32380a53cc33c980754cff46b3880a7317dd6e783f523b986aea91a</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19536024</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1785513066</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.405961</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0xa0c8d19ccd8222fe5808f3173eb4463c8de341ddcfcb086f400632089e4f0be4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>50.36</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.3375</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785497556</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>149.214815</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0x284f0b4a1de283358a3577badffac14ecc5afcfdc28ce21985a9cb86481ba6cc</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x6d158A0b6c9Df0483460f6a656673630210CAA4a</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.4463</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Rodina Moskva vs Rostov FK</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Rodina Moskva</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Rostov FK</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xc2ed80c842ab0c1d24361f465ff9c0b8137d5178739873b6e3325008d77dd204</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19536024</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1785497412</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>224.089636</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x82023bc913cac320bbcec8856b93c61ced3824bae2ff614f7aeb447196f63721</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>139.07045</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.7913</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1785492025</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>175.760442</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0xb79b0374865c7617b60514b2180feb26aead2aaca0895843000b71787d8212f5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>38.81386</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.7913</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785492024</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>49.053852</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>0x35c722e47edc576e91fff2a56006e70c47630baaf10fd0a9c8c7187b33e14e24</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>1.3113</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Premier League</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny vs Spartak Moskva</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Spartak Moskva</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>0xba2ac566f21d9b66fba41da0a24a5d93737f4a0c2789de13002227a82662899c</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>L19537277</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>1785344429</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>1785691800</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>3.212851</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premier League/trades.xlsx
+++ b/data/sxbet/ligas/Premier League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x1638d462ac081048e75f74389a4ff26e18b1ae1b526d3aeb9de1440589cd1e5d</t>
+          <t>0x71c680237c10938d6ff2f86cc1506136ea79cfb5efe6afba6ae391aeee4bd540</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>242.37998</t>
+          <t>110.53</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785522300</t>
+          <t>1785578189</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>336.638861</t>
+          <t>245.622222</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xbb7e9ff01a18bfc8edad554bb31f15afc9af81a591df798303c216a31f4f60a2</t>
+          <t>0x9befad38052d4ca6318a4605dbb41c5104b3b7d0effd979d0accdf78a9b920d2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.87</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3912</t>
+          <t>1.3475</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
+          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785519268</t>
+          <t>1785578188</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>109.571885</t>
+          <t>194.935252</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xb20c524d4e546a7083e83d50954cb82e74d2f35919a693305ef85bcd1297f018</t>
+          <t>0x3bd55ed63a8eaef652a1be74a03447a94d7f5c35e746d98a3837f7b0fa325a1b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.81967</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -787,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+          <t>0xd87e3e74d56c50a95f7eeab8f4e9093ec05b11e3354fb707ffcb563eeb3c5ea4</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785519268</t>
+          <t>1785578188</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>9.99219</t>
+          <t>175.277778</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,59 +867,67 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x4f0a3bc80edb843b0944d88bf4e31147f77d117de6bec90e861ee3f30e05ab04</t>
+          <t>0x19ad74f9aa58d0d1fe6231c86d3c37a94a7ebc8c40fb4bb83351e7bf0c42c216</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>Premier League</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785519266</t>
+          <t>1785578187</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>25.18451</t>
+          <t>206.139535</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x5ba31b6e54e59ca06de6605e21a3984e6bef3be97c4a38cb1fef0f420c3c5762</t>
+          <t>0x7d2baf055557c5e62d28cd672a372c6bd91f6bf5dfe4597861420643aeff9dad</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -971,7 +987,11 @@
           <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>5</t>
@@ -979,43 +999,47 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Premier League</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1064,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785517580</t>
+          <t>1785578167</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>9.111617</t>
+          <t>23.255814</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,59 +1091,67 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x34ae51184c54f771408cd03c9262de0e4ea1554f41b9cf4d3f7f2c5d4d746850</t>
+          <t>0xe2f3c80f061596dc0f213aaf63fc60ce9d354acd8c210edef40ee8fca220d9d9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.93611</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Premier League</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1176,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785517575</t>
+          <t>1785578165</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>25.3961</t>
+          <t>23.255814</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,31 +1203,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x7029f30f1995c9929d909d63df9f8e25356451c2543674cd96d9a354775d1cd1</t>
+          <t>0x22d1460f011136dbb3ed1cf16264fc07412888a881d4399ed4e7b633106c77ae</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -1203,27 +1243,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Rodina Moskva vs Rostov FK</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Rostov FK</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x79bda80ec32380a53cc33c980754cff46b3880a7317dd6e783f523b986aea91a</t>
+          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19536024</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1248,17 +1288,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785513066</t>
+          <t>1785578149</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.405961</t>
+          <t>65.162791</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,7 +1315,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xa0c8d19ccd8222fe5808f3173eb4463c8de341ddcfcb086f400632089e4f0be4</t>
+          <t>0xe6d907e5a15573780e8a153c25710ac68b05a2da9c440ce133df93c1b6371fad</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1290,22 +1330,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>50.36</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3375</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1315,27 +1355,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1360,17 +1400,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785497556</t>
+          <t>1785578147</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>149.214815</t>
+          <t>103.023256</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,39 +1427,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x284f0b4a1de283358a3577badffac14ecc5afcfdc28ce21985a9cb86481ba6cc</t>
+          <t>0x904a6c948bf4753c9e103e3afc8a7f4fb60c83a95390dade4f5f80838f2a6201</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x6d158A0b6c9Df0483460f6a656673630210CAA4a</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>594.4048</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.6625</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -1427,27 +1459,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Rodina Moskva vs Rostov FK</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Rostov FK</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xc2ed80c842ab0c1d24361f465ff9c0b8137d5178739873b6e3325008d77dd204</t>
+          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19536024</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1472,17 +1504,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785497412</t>
+          <t>1785578076</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>224.089636</t>
+          <t>897.214792</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,7 +1531,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x82023bc913cac320bbcec8856b93c61ced3824bae2ff614f7aeb447196f63721</t>
+          <t>0xeaa0f12279579996121f820f6e7c355f29cc7a7c0aff9e0d45b192a79bb86d53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1510,17 +1542,17 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>139.07045</t>
+          <t>422.63563</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7913</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1546,7 +1578,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1576,7 +1608,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785492025</t>
+          <t>1785578075</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1586,7 +1618,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>175.760442</t>
+          <t>753.025621</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,31 +1635,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xb79b0374865c7617b60514b2180feb26aead2aaca0895843000b71787d8212f5</t>
+          <t>0xe0818cb9f098e011b143578453eadde11363dedcc95f61e9dfca94267932d2cf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>38.81386</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7913</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CSKA Moscow -1</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -1650,7 +1690,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1680,7 +1720,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785492024</t>
+          <t>1785572887</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1730,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>49.053852</t>
+          <t>20.464286</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,110 +1747,4150 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>0xdae6a6bc9c468e345de6b0edd818d404c5d319a8b35d8b8e089f27c055c389b5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>108.62998</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.7975</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0x250c9978ebf5b011075be1d4db3f8d11c84ae4775b2a15381141c2041819671d</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785572661</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>136.213141</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x8287809c6ecbf4350c5b00a693999a7413ec85bf151e6bc30a165f00a63e0841</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>11.39998</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.7138</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Dynamo Moscow</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0xd2c373d98f28160b1937cb16fc225505947dd2558aed807adb6793d0ba065168</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19536935</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785572520</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785606300</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>15.971951</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x3b18e7fae3a0845fdb30a3cbe728a545cae4e662d0b4f73499445c8c15b3fc40</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785571166</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>29.411765</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x74da0033cbaaf0989652d45e0a379a053226dca51e774fe8f3d59364a7ed7bc3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21.9974</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.7462</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785571136</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>29.477253</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0xdf6e0cf8b56844dd97ec7cd857e88927c45b93f08b350ac9344b7a0606e045b8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>52.31835</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.7462</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785571135</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>70.108342</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0x018d60ff481049c67bba92e9b54e0d55c42b86a5d701c0b1c584e9807ee17e54</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>14.89036</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785571135</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>87.590353</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0xa5cc97a62584698f6c4048c5f24e84a8eadf70fd65b8935042102ef7c64fb9d8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>33.69787</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.5762</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0xeb29ac30b54329d5d60f9106332c47c7d06e00b17061f03af8f7e4b413a058ba</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785571067</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>58.477866</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0xf321b64477a115c8937a87a1a8313c82a213b8e568c8f88293a4375fba41be54</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.4612</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x3890375e41e397b7fd55fb869bda99e7fceb1ca0319fe030519bd2ec2cf5bc31</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19536924</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1785567916</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785598200</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2.233062</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0xe3ddd7c883204ad1dba275364ab1e46eb717f308b3dedc5acbd7703d980bec00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.7462</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1785563385</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>6.700141</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0xa4c6ae8963dfa3b202fe6ce8ce74f74e1dbf632ba3fc5ac6cee71b986816c930</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>77.76784</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.7425</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1785563353</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>104.737832</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x841657eb70bcebb4ab52934f0882d697225406f5e7fd8417bc066ef32cfd9f3f</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1785563065</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0xf274d715150d62a93d353cede0f6ff9c88848ac391602271e47187d10e35b365</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1785563064</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2.909091</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0xf8e15936a562a6c53c3f0b156df3f4beef97db21efe52a96112e59b7b71d2cfc</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>45.9</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785562017</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>133.527273</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0x31383c91bcc01015e13e5fd2b9bea5aca6c5af939719601af5d89e0d14f917d1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>16.28</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785561847</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>35.2</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x62d0c1650da9a9f20785ab148cd57757523f593981c50f9121d975d5671dc22c</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>11.86</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.345</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785561830</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>34.376812</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0xca8103b7c29655e3359ce0c76ab74b1e550d22a25b2697a62f009036198b340d</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785561684</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>29.411765</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0xd2b6ca67a5a2d819fc0cf69e7b7cb17aef0d37ea042ab1d803ea19a79869cf1c</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>15.91241</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785561659</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>93.602412</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x9df3204fd72e0052ebf44ed8084dee18335fa60165de967589f7ffece734f21d</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x8AaDb828882f34790D0C35aE0534a6BbDDA6ad19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785561561</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>21.621622</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x1c651915969f4f1991cb4f8083b94c18de450a29ab1d239f29fd2136f09013cd</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>39.53998</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.7138</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785559258</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>55.39752</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0xfe4e061b2e2e2540fd50c22f993ed8e84c7d22f3208b337d5a326d6444353f09</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>97.43997</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.7837</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0x5b5b30e2f6739fc9828801a4bc6c1fd66d2d048516210562005b195dab2ed7e8</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785559257</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>124.325321</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x08024130d9cb2665d1fada581c354f0d9912d9be188b8a5b5cd319c76fc8f84b</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.00083</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.7138</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785559257</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>0.001163</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x7a11de4f80dc40500c7c27e609aa7ce468977e4b318ea22ee056badb255acac0</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>23.05</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.2775</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19536924</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785554288</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785598200</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>83.063063</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x13a6ce7009e637abe73138bc7868471610982f652ed68f38fbb93a4e68405e6c</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.2775</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19536924</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785552612</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785598200</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>18.018018</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x17588dd455f17e31e06c55e5d5c91052a57c1fc2c2711a0891e74386a507ec57</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.2775</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19536924</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785552583</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785598200</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>52.612613</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x7e4e77fa047e471fb7a25555ab8b596db1c260554e819bf1e556c3fb95efcdad</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>63.81998</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.7125</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785550426</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>89.571902</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0xe168538382bb9379f973bea17e97bdbec6d33bf8f1675b71dfc9f45ecde2301e</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.2775</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19536924</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785549278</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785598200</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>18.018018</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0x01f52f51af10033e9f1c42cddafc3bf0296939cdfd57ee81fc03f9b4ce79db99</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>15.93</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.2775</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19536924</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785549255</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785598200</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>57.405405</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x1638d462ac081048e75f74389a4ff26e18b1ae1b526d3aeb9de1440589cd1e5d</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>242.37998</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Dynamo Moscow</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19536935</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785522300</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785606300</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>336.638861</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0xbb7e9ff01a18bfc8edad554bb31f15afc9af81a591df798303c216a31f4f60a2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>42.87</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.3912</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785519268</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>109.571885</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0xb20c524d4e546a7083e83d50954cb82e74d2f35919a693305ef85bcd1297f018</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6.81967</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.6825</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785519268</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>9.99219</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x4f0a3bc80edb843b0944d88bf4e31147f77d117de6bec90e861ee3f30e05ab04</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13.82</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.5488</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785519266</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>25.18451</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x5ba31b6e54e59ca06de6605e21a3984e6bef3be97c4a38cb1fef0f420c3c5762</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.5488</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785517580</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>9.111617</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x34ae51184c54f771408cd03c9262de0e4ea1554f41b9cf4d3f7f2c5d4d746850</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>13.93611</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.5488</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785517575</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>25.3961</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x7029f30f1995c9929d909d63df9f8e25356451c2543674cd96d9a354775d1cd1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.7113</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Rodina Moskva vs Rostov FK</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Rodina Moskva</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Rostov FK</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x79bda80ec32380a53cc33c980754cff46b3880a7317dd6e783f523b986aea91a</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19536024</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785513066</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1.405961</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0xa0c8d19ccd8222fe5808f3173eb4463c8de341ddcfcb086f400632089e4f0be4</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>50.36</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.3375</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19536035</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785497556</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785582000</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>149.214815</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x284f0b4a1de283358a3577badffac14ecc5afcfdc28ce21985a9cb86481ba6cc</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x6d158A0b6c9Df0483460f6a656673630210CAA4a</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.4463</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Rodina Moskva vs Rostov FK</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Rodina Moskva</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Rostov FK</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0xc2ed80c842ab0c1d24361f465ff9c0b8137d5178739873b6e3325008d77dd204</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19536024</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785497412</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785517200</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>224.089636</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x82023bc913cac320bbcec8856b93c61ced3824bae2ff614f7aeb447196f63721</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>139.07045</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.7913</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785492025</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>175.760442</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0xb79b0374865c7617b60514b2180feb26aead2aaca0895843000b71787d8212f5</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>38.81386</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.7913</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785492024</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>49.053852</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>0x35c722e47edc576e91fff2a56006e70c47630baaf10fd0a9c8c7187b33e14e24</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>1.3113</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Premier League</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny vs Spartak Moskva</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Spartak Moskva</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>0xba2ac566f21d9b66fba41da0a24a5d93737f4a0c2789de13002227a82662899c</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>L19537277</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>1785344429</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>1785691800</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>3.212851</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premier League/trades.xlsx
+++ b/data/sxbet/ligas/Premier League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V131"/>
+  <dimension ref="A1:V132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x50ae7a52a15efcf1c422c41197e194a91af4acb58e614d778935d3d064b16181</t>
+          <t>0x8c779320e758724f0763d70d66151134fb086c1e1a7a8eaf3324b2d1c7d2f063</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad -0.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xaa9700965af19b33d958192d1e341e976e37028b7fa61b0d892a1b51c842807b</t>
+          <t>0xd2c373d98f28160b1937cb16fc225505947dd2558aed807adb6793d0ba065168</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785606766</t>
+          <t>1785610673</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>14.760148</t>
+          <t>6.10687</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x7a432131da1edd8071f1eb7ad6d161c2aa3955629e87b1e9d75eec8c97545a0a</t>
+          <t>0x50ae7a52a15efcf1c422c41197e194a91af4acb58e614d778935d3d064b16181</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>157.62</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad -0.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -690,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
+          <t>0xaa9700965af19b33d958192d1e341e976e37028b7fa61b0d892a1b51c842807b</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785605951</t>
+          <t>1785606766</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>523.219917</t>
+          <t>14.760148</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,28 +755,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xd0061cc526a8d9b88b00729b269727277b0829533f7989113f37fb4f3a6e354f</t>
+          <t>0x7a432131da1edd8071f1eb7ad6d161c2aa3955629e87b1e9d75eec8c97545a0a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18.77999</t>
+          <t>157.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -794,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xe8207537e82b7cc6c2d40b1ffb94fb6a1298e8ffae224ad112dd145d2479d140</t>
+          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -824,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785605002</t>
+          <t>1785605951</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>29.63312</t>
+          <t>523.219917</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xed19f145677d00a1f377e327de7701c987d2a801382c985554f3b5246d4f7574</t>
+          <t>0xd0061cc526a8d9b88b00729b269727277b0829533f7989113f37fb4f3a6e354f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -859,19 +867,15 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>18.77999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.6338</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -879,26 +883,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>FC Baltika Kaliningrad</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Dynamo Moscow</t>
@@ -906,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x2634a9ad4709864d52fc8aa66fba0d772c164035502c70501d9eec4578d50acc</t>
+          <t>0xe8207537e82b7cc6c2d40b1ffb94fb6a1298e8ffae224ad112dd145d2479d140</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785604611</t>
+          <t>1785605002</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>154.646617</t>
+          <t>29.63312</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,12 +963,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xfc054e64f38b9eb4b1b012b19f4f9aa56fd4806dd6173dd23f29cb17367aa31d</t>
+          <t>0xed19f145677d00a1f377e327de7701c987d2a801382c985554f3b5246d4f7574</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>51.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7563</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1003,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
+          <t>0x2634a9ad4709864d52fc8aa66fba0d772c164035502c70501d9eec4578d50acc</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785604104</t>
+          <t>1785604611</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6.61157</t>
+          <t>154.646617</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xf05f75588bcd4ac061fc839cdafce4772aae26056ae40d8c6134f8592718fb9e</t>
+          <t>0xfc054e64f38b9eb4b1b012b19f4f9aa56fd4806dd6173dd23f29cb17367aa31d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1090,22 +1090,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>387.31856</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.7563</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x9125ce6f5ed52866b9368acc8e59eaffa5f02b8d5d4cd6bde41a6a1aaf05c16a</t>
+          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785603814</t>
+          <t>1785604104</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1526.378562</t>
+          <t>6.61157</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,12 +1187,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xbc831519a8d27b040d43b5495628a8039bdd1bb9deed0b72e68bbec6ab394032</t>
+          <t>0xf05f75588bcd4ac061fc839cdafce4772aae26056ae40d8c6134f8592718fb9e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1202,22 +1202,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.19999</t>
+          <t>387.31856</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xa99b14a45dd025e0d0b51f2a7021a6ce34c45565608d4ed6a189bdd8dfee08d3</t>
+          <t>0x9125ce6f5ed52866b9368acc8e59eaffa5f02b8d5d4cd6bde41a6a1aaf05c16a</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785603674</t>
+          <t>1785603814</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>5.844731</t>
+          <t>1526.378562</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,31 +1299,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x2279e851617cc78ef830ec1d05fd54bbdd2b673d8932991cfbb4cf20008040c8</t>
+          <t>0xbc831519a8d27b040d43b5495628a8039bdd1bb9deed0b72e68bbec6ab394032</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>3.19999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -1346,7 +1354,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x84855b76b3233b3863b628dae07980f03631d882c2ff3527cb6d8157953600b2</t>
+          <t>0xa99b14a45dd025e0d0b51f2a7021a6ce34c45565608d4ed6a189bdd8dfee08d3</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785603599</t>
+          <t>1785603674</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>76.469274</t>
+          <t>5.844731</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,39 +1411,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x22a61f4e6ccd6958df2fbd2e12f0b0760e9ecc0c9b8ad8f529059ae7deaa5605</t>
+          <t>0x2279e851617cc78ef830ec1d05fd54bbdd2b673d8932991cfbb4cf20008040c8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7188</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -1443,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
+          <t>0x84855b76b3233b3863b628dae07980f03631d882c2ff3527cb6d8157953600b2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785600110</t>
+          <t>1785603599</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>6.956522</t>
+          <t>76.469274</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xc38ef3f3b6d17f49fde86d0c249d5198de659a285ba5e66f9e5d30702b1539ad</t>
+          <t>0x22a61f4e6ccd6958df2fbd2e12f0b0760e9ecc0c9b8ad8f529059ae7deaa5605</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>151.58</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785600100</t>
+          <t>1785600110</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>210.893913</t>
+          <t>6.956522</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,31 +1627,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x0ac02cd68cef7f84b9d5edb2b42052b1581ab555504ea9eb7599dc3881e3ae7a</t>
+          <t>0xc38ef3f3b6d17f49fde86d0c249d5198de659a285ba5e66f9e5d30702b1539ad</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14.82999</t>
+          <t>151.58</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6475</t>
+          <t>1.7188</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -1659,27 +1667,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x48039cdeb89ebeb5a381396af9889bb029cca38a9035853205d890164d76b1e6</t>
+          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1712,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785597306</t>
+          <t>1785600100</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>22.903459</t>
+          <t>210.893913</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,28 +1739,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x6d5b2bcf883aa8f56cc1543e99253fb8badd13a550153724bea18a68328b3edc</t>
+          <t>0x0ac02cd68cef7f84b9d5edb2b42052b1581ab555504ea9eb7599dc3881e3ae7a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14.82999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8788</t>
+          <t>1.6475</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1778,7 +1786,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x4ebbf978346ce1ea467975cc8563aeb19503b54fbc259dee4316cf0b7c0b5070</t>
+          <t>0x48039cdeb89ebeb5a381396af9889bb029cca38a9035853205d890164d76b1e6</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1816,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785597145</t>
+          <t>1785597306</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1826,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5.6899</t>
+          <t>22.903459</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,18 +1843,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x127fe57658e163511b1474b93d7cf756021956ac9bca4584ad6af7c64077836d</t>
+          <t>0x6d5b2bcf883aa8f56cc1543e99253fb8badd13a550153724bea18a68328b3edc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14.63973</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1912,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785597104</t>
+          <t>1785597145</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>16.659721</t>
+          <t>5.6899</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,18 +1947,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x8025258561a6773ef950e12d7e2d5512dc21ca44c1b37a63b7e1125f3c80a7c4</t>
+          <t>0x127fe57658e163511b1474b93d7cf756021956ac9bca4584ad6af7c64077836d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14.63973</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2016,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785596844</t>
+          <t>1785597104</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2034,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>5.6899</t>
+          <t>16.659721</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,18 +2051,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x78f2cf0c44a1f9226c252b915c49a139e2cabfde0061a719e26c996fa1bbbeac</t>
+          <t>0x8025258561a6773ef950e12d7e2d5512dc21ca44c1b37a63b7e1125f3c80a7c4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>213.36406</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2120,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785596828</t>
+          <t>1785596844</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2130,7 +2138,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>242.804051</t>
+          <t>5.6899</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,39 +2155,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x5c792d7ccdce5d1dcc92bb439a1c386db3cdc678bf74f30175c5605f1bcee1c6</t>
+          <t>0x78f2cf0c44a1f9226c252b915c49a139e2cabfde0061a719e26c996fa1bbbeac</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>110.26999</t>
+          <t>213.36406</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Dynamo Dagestan Makhachkala +1</t>
-        </is>
-      </c>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xae5fbc672993d49fa7942061b539cb2fc8ebf0617f93d35cbeb337ad8744dea1</t>
+          <t>0x4ebbf978346ce1ea467975cc8563aeb19503b54fbc259dee4316cf0b7c0b5070</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785596769</t>
+          <t>1785596828</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>151.31388</t>
+          <t>242.804051</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,31 +2259,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x770475a22a747562c30442cf508e4c41e1186276aa0f531ce19cdaa7665217c7</t>
+          <t>0x5c792d7ccdce5d1dcc92bb439a1c386db3cdc678bf74f30175c5605f1bcee1c6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x869E0d5a56DC19f2A97743B65A2CD60b8470152F</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>110.26999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala +1</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -2291,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+          <t>0xae5fbc672993d49fa7942061b539cb2fc8ebf0617f93d35cbeb337ad8744dea1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2336,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785595958</t>
+          <t>1785596769</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>19.230769</t>
+          <t>151.31388</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,39 +2371,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x235bda23b440cf84c9236798e7a0fbf2c45cee263fbece7f20c160066960939e</t>
+          <t>0x770475a22a747562c30442cf508e4c41e1186276aa0f531ce19cdaa7665217c7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x869E0d5a56DC19f2A97743B65A2CD60b8470152F</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25.34</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd87e3e74d56c50a95f7eeab8f4e9093ec05b11e3354fb707ffcb563eeb3c5ea4</t>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785595503</t>
+          <t>1785595958</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>422.333333</t>
+          <t>19.230769</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,7 +2475,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xa81148619186b65d428a0ab1d5db583edc7e6abb8ec4b50e95b4141c37af730d</t>
+          <t>0x235bda23b440cf84c9236798e7a0fbf2c45cee263fbece7f20c160066960939e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>25.34</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785595501</t>
+          <t>1785595503</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>422.333333</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2587,7 +2587,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x4311b0c91c1e0cca14112e39dc165fb2a99f6a11ca9a89047e34ad1cb640d6b3</t>
+          <t>0xa81148619186b65d428a0ab1d5db583edc7e6abb8ec4b50e95b4141c37af730d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785595499</t>
+          <t>1785595501</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>435.166667</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2699,12 +2699,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x95636b08910b61970464a5fb5bb180432ebfb98e38177a7ebcca4a09b973ed40</t>
+          <t>0x4311b0c91c1e0cca14112e39dc165fb2a99f6a11ca9a89047e34ad1cb640d6b3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8b0c1cadD582567253C6e5F04361F059619f2f06</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2714,22 +2714,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3925</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0xd87e3e74d56c50a95f7eeab8f4e9093ec05b11e3354fb707ffcb563eeb3c5ea4</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785595382</t>
+          <t>1785595499</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2.547771</t>
+          <t>435.166667</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,12 +2811,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x7d6d6d79ceff309c95f350345d24a4a049f0469132844a7e672d7642aa2fbb26</t>
+          <t>0x95636b08910b61970464a5fb5bb180432ebfb98e38177a7ebcca4a09b973ed40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x8b0c1cadD582567253C6e5F04361F059619f2f06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>105.38</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.3925</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785595337</t>
+          <t>1785595382</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1453.517241</t>
+          <t>2.547771</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,12 +2923,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x74f88bd94a20141b2f689fbc9ee79cf2ad4ac87d15231b684850e3599184da52</t>
+          <t>0x7d6d6d79ceff309c95f350345d24a4a049f0469132844a7e672d7642aa2fbb26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x814d79A9940CbC5Af4C19cAa118EC065a77CD31f</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2938,39 +2938,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>105.38</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4312</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>CSKA Moscow</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>CSKA Moscow</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Krylia Sovetov</t>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785595294</t>
+          <t>1785595337</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>18.550725</t>
+          <t>1453.517241</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3035,12 +3035,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xea47e5e3f4d871a56d5cc47a9c4a1ac2fef6617d5149bed973c0c27e341338d9</t>
+          <t>0x74f88bd94a20141b2f689fbc9ee79cf2ad4ac87d15231b684850e3599184da52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x814d79A9940CbC5Af4C19cAa118EC065a77CD31f</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3050,22 +3050,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>181.67908</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.1187</t>
+          <t>1.4312</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785594965</t>
+          <t>1785595294</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1529.929095</t>
+          <t>18.550725</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3147,12 +3147,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xbf4661a11f952621b4227333cad433ff5cf2c3675620b42b2ccc13e871dc27a0</t>
+          <t>0xea47e5e3f4d871a56d5cc47a9c4a1ac2fef6617d5149bed973c0c27e341338d9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8b0c1cadD582567253C6e5F04361F059619f2f06</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3162,22 +3162,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>181.67908</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.1187</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x7f8975f5bd29ad9963300500e7270929609de63bb399f3d8760b7e6131ddcf98</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785594922</t>
+          <t>1785594965</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1.985112</t>
+          <t>1529.929095</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3259,12 +3259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x1c5226d2320fb26e307a8eb3ec872719f375af1337b3c17f6684cf399e639635</t>
+          <t>0xbf4661a11f952621b4227333cad433ff5cf2c3675620b42b2ccc13e871dc27a0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8b0c1cadD582567253C6e5F04361F059619f2f06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.7188</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3299,27 +3299,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
+          <t>0x7f8975f5bd29ad9963300500e7270929609de63bb399f3d8760b7e6131ddcf98</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3344,17 +3344,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785594048</t>
+          <t>1785594922</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>6.956522</t>
+          <t>1.985112</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x4c9cc9ccaed8c6a6c550ae2f4e3650e53a05908358942c69cad0831163b816a1</t>
+          <t>0x1c5226d2320fb26e307a8eb3ec872719f375af1337b3c17f6684cf399e639635</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785594029</t>
+          <t>1785594048</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>62.358261</t>
+          <t>6.956522</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3483,7 +3483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xd41ffcf00a30cf05017e50b4fafa0af98ebf4cb2c973b0c7b07694d0d3176f23</t>
+          <t>0x4c9cc9ccaed8c6a6c550ae2f4e3650e53a05908358942c69cad0831163b816a1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3498,22 +3498,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>307.43999</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.7188</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3523,27 +3523,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xd1cf347863a77aa700b93801eb228f9123026b23f36d67a3b0ffd65a9abe81c0</t>
+          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3568,17 +3568,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785593346</t>
+          <t>1785594029</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>492.889764</t>
+          <t>62.358261</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3595,7 +3595,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x7f2c88e28d01d35404ba595fce0e3b09c96ec24de31112619729efb09352b57b</t>
+          <t>0xd41ffcf00a30cf05017e50b4fafa0af98ebf4cb2c973b0c7b07694d0d3176f23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3610,22 +3610,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>34.89999</t>
+          <t>307.43999</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.7212</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x51e9cf87343115ee189ed1aba6feb100a49e6885fd6d113601d07829abebf384</t>
+          <t>0xd1cf347863a77aa700b93801eb228f9123026b23f36d67a3b0ffd65a9abe81c0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>48.388201</t>
+          <t>492.889764</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3707,31 +3707,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xf64924be42de3b43b03c8cff95357c3d85934d1dadd99c0151718a6c68c622f3</t>
+          <t>0x7f2c88e28d01d35404ba595fce0e3b09c96ec24de31112619729efb09352b57b</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xCA5FE59CB511e3B15948861b939f0CA0BC22f990</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>34.89999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.7212</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -3739,27 +3747,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0x51e9cf87343115ee189ed1aba6feb100a49e6885fd6d113601d07829abebf384</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3784,17 +3792,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785592840</t>
+          <t>1785593346</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.649485</t>
+          <t>48.388201</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3811,39 +3819,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xc95d3e9241a8ab5ab7b7dcf5d2a951b0d9f4d9707cccf2a8e6cd1ea1d80d2439</t>
+          <t>0xf64924be42de3b43b03c8cff95357c3d85934d1dadd99c0151718a6c68c622f3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xCA5FE59CB511e3B15948861b939f0CA0BC22f990</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15.10999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -3851,27 +3851,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xd1cf347863a77aa700b93801eb228f9123026b23f36d67a3b0ffd65a9abe81c0</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3896,17 +3896,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785592835</t>
+          <t>1785592840</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>24.370952</t>
+          <t>1.649485</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3923,31 +3923,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xf8e021489ea1c7b0226fe5f713cd39f5736596eb8671400efbca9c4d5c8cb41a</t>
+          <t>0xc95d3e9241a8ab5ab7b7dcf5d2a951b0d9f4d9707cccf2a8e6cd1ea1d80d2439</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xCA5FE59CB511e3B15948861b939f0CA0BC22f990</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.10999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.6075</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -3955,27 +3963,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0xd1cf347863a77aa700b93801eb228f9123026b23f36d67a3b0ffd65a9abe81c0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4000,17 +4008,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785592813</t>
+          <t>1785592835</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1.646091</t>
+          <t>24.370952</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4027,39 +4035,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xc96fbe1aca4911173d2e73d29d24e82082f72c91fb2d9d22198f4e17b0daa7cc</t>
+          <t>0xf8e021489ea1c7b0226fe5f713cd39f5736596eb8671400efbca9c4d5c8cb41a</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xCA5FE59CB511e3B15948861b939f0CA0BC22f990</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>29.58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.8137</t>
+          <t>1.6075</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>CSKA Moscow -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x2412409c0dd32a8d9afa2868789771e8bd2fbb4ff00df2699b025196a4208fe6</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785592455</t>
+          <t>1785592813</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>36.35023</t>
+          <t>1.646091</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4139,7 +4139,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xb0d4d9e860a08d8a292bf7157c7e210af4e07fdd308da88048d016afd3a255e4</t>
+          <t>0xc96fbe1aca4911173d2e73d29d24e82082f72c91fb2d9d22198f4e17b0daa7cc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4164,29 +4164,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>CSKA Moscow -0.5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>CSKA Moscow</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>CSKA Moscow</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Krylia Sovetov</t>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+          <t>0x2412409c0dd32a8d9afa2868789771e8bd2fbb4ff00df2699b025196a4208fe6</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4251,7 +4251,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x83dc737ceb377e4b5b06cf4bec789a04964df61c68c148f31504279914da6ba2</t>
+          <t>0xb0d4d9e860a08d8a292bf7157c7e210af4e07fdd308da88048d016afd3a255e4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4266,22 +4266,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>37.34998</t>
+          <t>29.58</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.7412</t>
+          <t>1.8137</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CSKA Moscow -1</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785592440</t>
+          <t>1785592455</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>50.387831</t>
+          <t>36.35023</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x3bcc92e2ec706f2ceb301ed4c824be2e3e926245e15a2e493daf383993605e7a</t>
+          <t>0x83dc737ceb377e4b5b06cf4bec789a04964df61c68c148f31504279914da6ba2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>212.54</t>
+          <t>37.34998</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785592417</t>
+          <t>1785592440</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>286.731872</t>
+          <t>50.387831</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xbba29fda9dedca632ac108d9a69d5a0c157e4e8061cce4257f8b8ce4d3b67f56</t>
+          <t>0x3bcc92e2ec706f2ceb301ed4c824be2e3e926245e15a2e493daf383993605e7a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>136.35998</t>
+          <t>212.54</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785592408</t>
+          <t>1785592417</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>183.959501</t>
+          <t>286.731872</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4587,7 +4587,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x224ceaf34c69289e46cb33799c850a0aa119d1a3452f13001574ce16f9ab1e63</t>
+          <t>0xbba29fda9dedca632ac108d9a69d5a0c157e4e8061cce4257f8b8ce4d3b67f56</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4602,22 +4602,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>380.27565</t>
+          <t>136.35998</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.7412</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>CSKA Moscow -1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
+          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785592215</t>
+          <t>1785592408</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1728.525682</t>
+          <t>183.959501</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4699,7 +4699,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x487dc2b53bf8a100c2e3feb8bcb6a3d3a333ca75dabd3839c7910dfaa2e6bd23</t>
+          <t>0x224ceaf34c69289e46cb33799c850a0aa119d1a3452f13001574ce16f9ab1e63</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>149.43</t>
+          <t>380.27565</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785592193</t>
+          <t>1785592215</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>679.227273</t>
+          <t>1728.525682</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x1a77166bd82bda7e2b3f101a4630482c49539e60be95942f73b6c4975e472114</t>
+          <t>0x487dc2b53bf8a100c2e3feb8bcb6a3d3a333ca75dabd3839c7910dfaa2e6bd23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>385.83</t>
+          <t>149.43</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785592178</t>
+          <t>1785592193</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1734.067416</t>
+          <t>679.227273</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xe09ad43dd9944457aceae37ee59366c61bbac0d396f68771268284bd5c87d0c0</t>
+          <t>0x1a77166bd82bda7e2b3f101a4630482c49539e60be95942f73b6c4975e472114</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4938,22 +4938,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>387.25</t>
+          <t>385.83</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
+          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785592174</t>
+          <t>1785592178</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1015.737705</t>
+          <t>1734.067416</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5035,31 +5035,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xf88c88a29be02fb94a9dab0fbc4e2ed0bac224f88e9b4b779477e1490042e2ae</t>
+          <t>0xe09ad43dd9944457aceae37ee59366c61bbac0d396f68771268284bd5c87d0c0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.03999</t>
+          <t>387.25</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5813</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -5082,7 +5090,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x8ffd92622adb93bd2101fc238161617dbb8897d09ee6afc55f29307cb3793d05</t>
+          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5112,7 +5120,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785591692</t>
+          <t>1785592174</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5122,7 +5130,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1.78923</t>
+          <t>1015.737705</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5139,28 +5147,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x1ee1488fc31a3a0e48b798b5ac1dd5ecfb00e524f3206d2450e438d416d9c193</t>
+          <t>0xf88c88a29be02fb94a9dab0fbc4e2ed0bac224f88e9b4b779477e1490042e2ae</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>520.52997</t>
+          <t>1.03999</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.8825</t>
+          <t>1.5813</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5186,7 +5194,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x4141b7262e76b825e847b7193427b95d711fe2bb2c28b855bd078338d783a1b1</t>
+          <t>0x8ffd92622adb93bd2101fc238161617dbb8897d09ee6afc55f29307cb3793d05</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5216,7 +5224,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785590379</t>
+          <t>1785591692</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5226,7 +5234,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>589.83566</t>
+          <t>1.78923</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5243,7 +5251,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xe6e5db04c3d252eec750387fc6b8ce1112a01b303faef17214a4fd1beb91207d</t>
+          <t>0x1ee1488fc31a3a0e48b798b5ac1dd5ecfb00e524f3206d2450e438d416d9c193</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5254,12 +5262,12 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>520.52997</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.8825</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5275,27 +5283,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xa99b14a45dd025e0d0b51f2a7021a6ce34c45565608d4ed6a189bdd8dfee08d3</t>
+          <t>0x4141b7262e76b825e847b7193427b95d711fe2bb2c28b855bd078338d783a1b1</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5320,17 +5328,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785590151</t>
+          <t>1785590379</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>36.986111</t>
+          <t>589.83566</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5347,27 +5355,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x965a0a328480fa4a41790b4f7637b6a583f61eb86a2b8ed0fc0f9870bc65f420</t>
+          <t>0xe6e5db04c3d252eec750387fc6b8ce1112a01b303faef17214a4fd1beb91207d</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.2063</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5375,11 +5379,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -5387,27 +5387,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+          <t>0xa99b14a45dd025e0d0b51f2a7021a6ce34c45565608d4ed6a189bdd8dfee08d3</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5432,17 +5432,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785589316</t>
+          <t>1785590151</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>73.018182</t>
+          <t>36.986111</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5459,12 +5459,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x28afed33e94a59282b8d2c84464b244379f7d6408ba99eebcdfafd995420f4bd</t>
+          <t>0x965a0a328480fa4a41790b4f7637b6a583f61eb86a2b8ed0fc0f9870bc65f420</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5474,39 +5474,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>60.47996</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.8325</t>
+          <t>1.2063</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>CSKA Moscow</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>CSKA Moscow</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>Krylia Sovetov</t>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785588862</t>
+          <t>1785589316</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>72.648601</t>
+          <t>73.018182</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5571,31 +5571,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x60a2233a146993b8ac9fe21ae7d844b4dad360e92a15e78203e2cc6e0d5cc4a1</t>
+          <t>0x28afed33e94a59282b8d2c84464b244379f7d6408ba99eebcdfafd995420f4bd</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>60.47996</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.7388</t>
+          <t>1.8325</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -5618,7 +5626,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5648,7 +5656,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785587961</t>
+          <t>1785588862</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5658,7 +5666,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>6.768162</t>
+          <t>72.648601</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5675,18 +5683,18 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x9c46c5a0d8c22ad2368bb391449ddf09edaa96170ccb65a1f3ca65b25097b289</t>
+          <t>0x60a2233a146993b8ac9fe21ae7d844b4dad360e92a15e78203e2cc6e0d5cc4a1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>103.91983</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5752,7 +5760,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785587946</t>
+          <t>1785587961</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5762,7 +5770,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>140.669821</t>
+          <t>6.768162</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5779,54 +5787,46 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x18458bdae26217c9a02527ebde2e8fdfd56ad86d5959ef901d301f7f162955b6</t>
+          <t>0x9c46c5a0d8c22ad2368bb391449ddf09edaa96170ccb65a1f3ca65b25097b289</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x8FFa640b1a609341C606048226D609Caa3D8F534</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>103.91983</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.7388</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>CSKA Moscow</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>CSKA Moscow</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>Krylia Sovetov</t>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785587168</t>
+          <t>1785587946</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>32.59854</t>
+          <t>140.669821</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5891,31 +5891,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xd05d88b9fc84bf4104af718f1f40a9323b34ac84cf741c06ddc9f34886848b5e</t>
+          <t>0x18458bdae26217c9a02527ebde2e8fdfd56ad86d5959ef901d301f7f162955b6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0x8FFa640b1a609341C606048226D609Caa3D8F534</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>505.16901</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -5923,27 +5931,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xa33f025604fd2a2fc54933008b6c278b1d57959363cf2c1babb844c699caed0d</t>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5968,17 +5976,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785585935</t>
+          <t>1785587168</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>908.169007</t>
+          <t>32.59854</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5995,7 +6003,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xc5a381716ff4466fb74dd190e49d7675fbb8f26575dc66b9cd0f6bc083bbbf12</t>
+          <t>0xd05d88b9fc84bf4104af718f1f40a9323b34ac84cf741c06ddc9f34886848b5e</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6003,31 +6011,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>73.65</t>
+          <t>505.16901</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (6)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Over 6.0</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x584e346bab3cebc0c715fcf0640eb5290a5c0a96732e7e83570bd97ebba5d395</t>
+          <t>0xa33f025604fd2a2fc54933008b6c278b1d57959363cf2c1babb844c699caed0d</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785585070</t>
+          <t>1785585935</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1202.44898</t>
+          <t>908.169007</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6107,7 +6107,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x3d35c451671ff9eb43b21ae0b250eb75eee54546feaa62a1ca9b78b7fd6e0d27</t>
+          <t>0xc5a381716ff4466fb74dd190e49d7675fbb8f26575dc66b9cd0f6bc083bbbf12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>71.53</t>
+          <t>73.65</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785585067</t>
+          <t>1785585070</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1167.836735</t>
+          <t>1202.44898</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6219,31 +6219,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x8940dac2686c289f7c861dabf9fc00df95ca01be5b3ea13c3485603a628c17df</t>
+          <t>0x3d35c451671ff9eb43b21ae0b250eb75eee54546feaa62a1ca9b78b7fd6e0d27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>71.53</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>Under/Over (6)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Over 6.0</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -6251,27 +6259,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x3890375e41e397b7fd55fb869bda99e7fceb1ca0319fe030519bd2ec2cf5bc31</t>
+          <t>0x584e346bab3cebc0c715fcf0640eb5290a5c0a96732e7e83570bd97ebba5d395</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6296,17 +6304,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785583664</t>
+          <t>1785585067</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1.855856</t>
+          <t>1167.836735</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6323,39 +6331,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xec27e0788abf17d968f42b04eafa023a6eba129883cb1e3876be9d378a83e751</t>
+          <t>0x8940dac2686c289f7c861dabf9fc00df95ca01be5b3ea13c3485603a628c17df</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3Cd99B8d9ff9F970d873FD51Db34a241440516</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.6587</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -6363,27 +6363,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xeb29ac30b54329d5d60f9106332c47c7d06e00b17061f03af8f7e4b413a058ba</t>
+          <t>0x3890375e41e397b7fd55fb869bda99e7fceb1ca0319fe030519bd2ec2cf5bc31</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6408,17 +6408,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785583182</t>
+          <t>1785583664</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>12.144213</t>
+          <t>1.855856</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6435,12 +6435,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xb1960c7a23b3de34f30b49e815403305310b24201207e590f7ca2d78675dc84a</t>
+          <t>0xec27e0788abf17d968f42b04eafa023a6eba129883cb1e3876be9d378a83e751</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3Cd99B8d9ff9F970d873FD51Db34a241440516</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6450,22 +6450,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>104.68</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.6587</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x38e80927c0a6c6a6cc0e5fe3192052f0eca332106c22fed66bbabfe0bc9639ef</t>
+          <t>0xeb29ac30b54329d5d60f9106332c47c7d06e00b17061f03af8f7e4b413a058ba</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785581549</t>
+          <t>1785583182</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>178.940171</t>
+          <t>12.144213</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6547,31 +6547,39 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x35b45074731811f6a18d4f27b8e6bc36b2b4a7c5d4806c8dd65290c77c9c37cd</t>
+          <t>0xb1960c7a23b3de34f30b49e815403305310b24201207e590f7ca2d78675dc84a</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20.85187</t>
+          <t>104.68</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.2363</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -6594,7 +6602,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x601087387a28c77812b112d8474717401c18647e54d4756ab3fdba097f85ec37</t>
+          <t>0x38e80927c0a6c6a6cc0e5fe3192052f0eca332106c22fed66bbabfe0bc9639ef</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6624,7 +6632,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785581132</t>
+          <t>1785581549</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6634,7 +6642,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>88.261884</t>
+          <t>178.940171</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6651,28 +6659,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xfa50a9ed43bd66076a555f0ac40fc5b1a211bafe0d1b6da263a6b8eba4bcdf0e</t>
+          <t>0x35b45074731811f6a18d4f27b8e6bc36b2b4a7c5d4806c8dd65290c77c9c37cd</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>20.85187</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.2363</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6698,7 +6706,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
+          <t>0x601087387a28c77812b112d8474717401c18647e54d4756ab3fdba097f85ec37</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6728,7 +6736,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785580982</t>
+          <t>1785581132</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6738,7 +6746,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>4.721541</t>
+          <t>88.261884</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6755,23 +6763,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xb523260d447b81e1b44693f689118d4542dde7579c64b2178af4a1ea620d7f2f</t>
+          <t>0xfa50a9ed43bd66076a555f0ac40fc5b1a211bafe0d1b6da263a6b8eba4bcdf0e</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6802,7 +6810,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
+          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6832,7 +6840,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785580513</t>
+          <t>1785580982</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6842,7 +6850,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>8.281573</t>
+          <t>4.721541</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6859,39 +6867,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xcc85f1682b7ccf4520cfb9a48b5664a79d5fdf8a5e44b6159877d3dbea266eb7</t>
+          <t>0xb523260d447b81e1b44693f689118d4542dde7579c64b2178af4a1ea620d7f2f</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>235.54997</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti +1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x601087387a28c77812b112d8474717401c18647e54d4756ab3fdba097f85ec37</t>
+          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785580491</t>
+          <t>1785580513</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>302.958161</t>
+          <t>8.281573</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6971,7 +6971,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x21084d8b56382ab72d2397bc760b32e74b434d258e1a7b26a8d608ca837c7bf5</t>
+          <t>0xcc85f1682b7ccf4520cfb9a48b5664a79d5fdf8a5e44b6159877d3dbea266eb7</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6979,23 +6979,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>214.19601</t>
+          <t>235.54997</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti +1</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -7018,7 +7026,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
+          <t>0x601087387a28c77812b112d8474717401c18647e54d4756ab3fdba097f85ec37</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7058,7 +7066,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>354.776</t>
+          <t>302.958161</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7075,7 +7083,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x0f1ec682294b81b957ec9320ab2ba03a785eb144eaa7015bc6aa0c7d36dc9784</t>
+          <t>0x21084d8b56382ab72d2397bc760b32e74b434d258e1a7b26a8d608ca837c7bf5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7083,19 +7091,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>60.29469</t>
+          <t>214.19601</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.3062</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7103,26 +7107,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>Akron Tolyatti</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>Rubin Kazan</t>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785580474</t>
+          <t>1785580491</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>196.88062</t>
+          <t>354.776</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7187,12 +7187,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xacb367c0fc88d2c85ecb600f69dd10c67b60f8988daff7659225967aa379d176</t>
+          <t>0x0f1ec682294b81b957ec9320ab2ba03a785eb144eaa7015bc6aa0c7d36dc9784</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60.29469</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785580472</t>
+          <t>1785580474</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>16.326531</t>
+          <t>196.88062</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7299,12 +7299,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xe3a1a841a351bcdd8a484cd64114f2d7db1dfd75800cd3ee134233667db90ea6</t>
+          <t>0xacb367c0fc88d2c85ecb600f69dd10c67b60f8988daff7659225967aa379d176</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785580471</t>
+          <t>1785580472</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>16.326531</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7411,7 +7411,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x45804ff4b428c2108aa52a14a28a1f369431ae728197068028893a8af476a7b4</t>
+          <t>0xe3a1a841a351bcdd8a484cd64114f2d7db1dfd75800cd3ee134233667db90ea6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785580441</t>
+          <t>1785580471</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>121.077551</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7523,7 +7523,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x0eb822189e746c5e95fe5853d2f4fc74971bb537879255ad9d205c8196d1a2eb</t>
+          <t>0x45804ff4b428c2108aa52a14a28a1f369431ae728197068028893a8af476a7b4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7538,22 +7538,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.4325</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Akron Tolyatti 0</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785580440</t>
+          <t>1785580441</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>118.774566</t>
+          <t>121.077551</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7635,12 +7635,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x2fab84ac790d16a69c18a7a9dd47379a135901c31ac1a4f1c3d6f7d3e92d3854</t>
+          <t>0x0eb822189e746c5e95fe5853d2f4fc74971bb537879255ad9d205c8196d1a2eb</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4325</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7665,24 +7665,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>Akron Tolyatti 0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>Akron Tolyatti</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>Rubin Kazan</t>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x19c474e600655dfbc3f44466abb293af14cd945496e841a711a52e75c96885db</t>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785580316</t>
+          <t>1785580440</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>11.627907</t>
+          <t>118.774566</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7747,7 +7747,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x70719f041d0bf5efce4a5ba7bfcad8d865f58d1176e9059a57d39a090e9cf2ba</t>
+          <t>0x2fab84ac790d16a69c18a7a9dd47379a135901c31ac1a4f1c3d6f7d3e92d3854</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785580314</t>
+          <t>1785580316</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7859,7 +7859,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xf591bb29dd4b46408f825e48edd0794dabb3d8fd69d8f446eb6d3902650c3b78</t>
+          <t>0x70719f041d0bf5efce4a5ba7bfcad8d865f58d1176e9059a57d39a090e9cf2ba</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785580312</t>
+          <t>1785580314</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x39ad701757f1d9ca28f9d14e317c6b9eeea74c3a6e4a465fb14c21a36372b243</t>
+          <t>0xf591bb29dd4b46408f825e48edd0794dabb3d8fd69d8f446eb6d3902650c3b78</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785580310</t>
+          <t>1785580312</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x036248e84feca2cdfc6fb53e4bc061d3eefed42a0092f926e8a1746b7a894a56</t>
+          <t>0x39ad701757f1d9ca28f9d14e317c6b9eeea74c3a6e4a465fb14c21a36372b243</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785580306</t>
+          <t>1785580310</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>33.651163</t>
+          <t>11.627907</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x1e50f9baf79081d66608d3a7ab5b5a987a6af5077945ef59e02797b63779d25e</t>
+          <t>0x036248e84feca2cdfc6fb53e4bc061d3eefed42a0092f926e8a1746b7a894a56</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785580305</t>
+          <t>1785580306</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>162.046512</t>
+          <t>33.651163</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8307,7 +8307,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x20fed495e61f16b787030a01fda248ac9b1440e2bff075e1455b047031b5be4c</t>
+          <t>0x1e50f9baf79081d66608d3a7ab5b5a987a6af5077945ef59e02797b63779d25e</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>107.79</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785580303</t>
+          <t>1785580305</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>250.674419</t>
+          <t>162.046512</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8419,7 +8419,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x5d4f9ea995b55daae2e64168f1979db64805dfdb2c066be9533eea41e19aa389</t>
+          <t>0x20fed495e61f16b787030a01fda248ac9b1440e2bff075e1455b047031b5be4c</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>107.79</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785580302</t>
+          <t>1785580303</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>49.511628</t>
+          <t>250.674419</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8531,7 +8531,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x58ec131ccccc4609dced3107a7a6729c4349b050ae43bd510e0bf2a0910eeaae</t>
+          <t>0x5d4f9ea995b55daae2e64168f1979db64805dfdb2c066be9533eea41e19aa389</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8539,15 +8539,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>74.15301</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8555,7 +8559,11 @@
           <t>Premier League</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -8608,7 +8616,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785580213</t>
+          <t>1785580302</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8618,7 +8626,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>130.093</t>
+          <t>49.511628</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8635,7 +8643,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xea3905fdcd9b1ad2193748b119a7e458bc170bfb7dcbd3c0a85908ea51ddb63b</t>
+          <t>0x58ec131ccccc4609dced3107a7a6729c4349b050ae43bd510e0bf2a0910eeaae</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8646,7 +8654,7 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>56.39022</t>
+          <t>74.15301</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8682,7 +8690,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+          <t>0x19c474e600655dfbc3f44466abb293af14cd945496e841a711a52e75c96885db</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8712,7 +8720,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785580212</t>
+          <t>1785580213</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8722,7 +8730,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>98.930211</t>
+          <t>130.093</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8739,7 +8747,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x950cdd981b49874d9c07780ab0f05a75c9eaa55c20022cda456f6529599d4534</t>
+          <t>0xea3905fdcd9b1ad2193748b119a7e458bc170bfb7dcbd3c0a85908ea51ddb63b</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8747,54 +8755,46 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>54.58929</t>
+          <t>56.39022</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.4013</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>Rubin Kazan</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Rubin Kazan</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>136.048075</t>
+          <t>98.930211</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8851,31 +8851,39 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x55854836a5bfee9cf8e7d0ab75b0581b46d221967750f4a25ecce99ddf563a3d</t>
+          <t>0x950cdd981b49874d9c07780ab0f05a75c9eaa55c20022cda456f6529599d4534</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>54.58929</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>1.4013</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -8883,27 +8891,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xed1f9246b9fc0972f71238e82ceef603b7365dad40f0d40c40e65009e4d8f1cf</t>
+          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8928,17 +8936,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785579621</t>
+          <t>1785580212</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>7.09217</t>
+          <t>136.048075</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8955,7 +8963,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x3e6fb1125ab2c5cf6dffe098637fd1759f20af5b957a55cc8ac4da659dd9263e</t>
+          <t>0x55854836a5bfee9cf8e7d0ab75b0581b46d221967750f4a25ecce99ddf563a3d</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9032,7 +9040,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785579619</t>
+          <t>1785579621</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -9059,18 +9067,18 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x4edfc8afb4d9319e7ca22a617ab98d44d9088cfb97b08b375820e1c2f75a54b7</t>
+          <t>0x3e6fb1125ab2c5cf6dffe098637fd1759f20af5b957a55cc8ac4da659dd9263e</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>26.74218</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9136,7 +9144,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785579591</t>
+          <t>1785579619</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9146,7 +9154,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>37.93217</t>
+          <t>7.09217</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9163,7 +9171,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xdd5efa16642d37a2f2b1a7e3b92e121d783c6088a705f8ed59b37491780656a1</t>
+          <t>0x4edfc8afb4d9319e7ca22a617ab98d44d9088cfb97b08b375820e1c2f75a54b7</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9174,7 +9182,7 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>30.97218</t>
+          <t>26.74218</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9240,7 +9248,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785579590</t>
+          <t>1785579591</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9250,7 +9258,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>43.93217</t>
+          <t>37.93217</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9267,7 +9275,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x71c680237c10938d6ff2f86cc1506136ea79cfb5efe6afba6ae391aeee4bd540</t>
+          <t>0xdd5efa16642d37a2f2b1a7e3b92e121d783c6088a705f8ed59b37491780656a1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9275,19 +9283,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>110.53</t>
+          <t>30.97218</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.705</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9295,11 +9299,7 @@
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -9307,27 +9307,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0xed1f9246b9fc0972f71238e82ceef603b7365dad40f0d40c40e65009e4d8f1cf</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9352,17 +9352,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785578189</t>
+          <t>1785579590</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>245.622222</t>
+          <t>43.93217</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9379,7 +9379,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x9befad38052d4ca6318a4605dbb41c5104b3b7d0effd979d0accdf78a9b920d2</t>
+          <t>0x71c680237c10938d6ff2f86cc1506136ea79cfb5efe6afba6ae391aeee4bd540</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9394,22 +9394,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>110.53</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785578188</t>
+          <t>1785578189</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>194.935252</t>
+          <t>245.622222</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9491,7 +9491,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x3bd55ed63a8eaef652a1be74a03447a94d7f5c35e746d98a3837f7b0fa325a1b</t>
+          <t>0x9befad38052d4ca6318a4605dbb41c5104b3b7d0effd979d0accdf78a9b920d2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9506,22 +9506,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.3475</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xd87e3e74d56c50a95f7eeab8f4e9093ec05b11e3354fb707ffcb563eeb3c5ea4</t>
+          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>175.277778</t>
+          <t>194.935252</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9603,7 +9603,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x19ad74f9aa58d0d1fe6231c86d3c37a94a7ebc8c40fb4bb83351e7bf0c42c216</t>
+          <t>0x3bd55ed63a8eaef652a1be74a03447a94d7f5c35e746d98a3837f7b0fa325a1b</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
+          <t>0xd87e3e74d56c50a95f7eeab8f4e9093ec05b11e3354fb707ffcb563eeb3c5ea4</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785578187</t>
+          <t>1785578188</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>206.139535</t>
+          <t>175.277778</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9715,12 +9715,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x7d2baf055557c5e62d28cd672a372c6bd91f6bf5dfe4597861420643aeff9dad</t>
+          <t>0x19ad74f9aa58d0d1fe6231c86d3c37a94a7ebc8c40fb4bb83351e7bf0c42c216</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785578167</t>
+          <t>1785578187</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>23.255814</t>
+          <t>206.139535</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9827,7 +9827,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xe2f3c80f061596dc0f213aaf63fc60ce9d354acd8c210edef40ee8fca220d9d9</t>
+          <t>0x7d2baf055557c5e62d28cd672a372c6bd91f6bf5dfe4597861420643aeff9dad</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785578165</t>
+          <t>1785578167</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9939,12 +9939,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x22d1460f011136dbb3ed1cf16264fc07412888a881d4399ed4e7b633106c77ae</t>
+          <t>0xe2f3c80f061596dc0f213aaf63fc60ce9d354acd8c210edef40ee8fca220d9d9</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785578149</t>
+          <t>1785578165</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>65.162791</t>
+          <t>23.255814</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10051,7 +10051,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0xe6d907e5a15573780e8a153c25710ac68b05a2da9c440ce133df93c1b6371fad</t>
+          <t>0x22d1460f011136dbb3ed1cf16264fc07412888a881d4399ed4e7b633106c77ae</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785578147</t>
+          <t>1785578149</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>103.023256</t>
+          <t>65.162791</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10163,7 +10163,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x904a6c948bf4753c9e103e3afc8a7f4fb60c83a95390dade4f5f80838f2a6201</t>
+          <t>0xe6d907e5a15573780e8a153c25710ac68b05a2da9c440ce133df93c1b6371fad</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10171,23 +10171,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>594.4048</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.6625</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -10210,7 +10218,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
+          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10240,7 +10248,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785578076</t>
+          <t>1785578147</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10250,7 +10258,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>897.214792</t>
+          <t>103.023256</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10267,7 +10275,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0xeaa0f12279579996121f820f6e7c355f29cc7a7c0aff9e0d45b192a79bb86d53</t>
+          <t>0x904a6c948bf4753c9e103e3afc8a7f4fb60c83a95390dade4f5f80838f2a6201</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10278,17 +10286,17 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>422.63563</t>
+          <t>594.4048</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.6625</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -10314,7 +10322,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10344,7 +10352,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785578075</t>
+          <t>1785578076</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10354,7 +10362,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>753.025621</t>
+          <t>897.214792</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10371,39 +10379,31 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0xe0818cb9f098e011b143578453eadde11363dedcc95f61e9dfca94267932d2cf</t>
+          <t>0xeaa0f12279579996121f820f6e7c355f29cc7a7c0aff9e0d45b192a79bb86d53</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>422.63563</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>CSKA Moscow -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785572887</t>
+          <t>1785578075</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>20.464286</t>
+          <t>753.025621</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10483,12 +10483,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0xdae6a6bc9c468e345de6b0edd818d404c5d319a8b35d8b8e089f27c055c389b5</t>
+          <t>0xe0818cb9f098e011b143578453eadde11363dedcc95f61e9dfca94267932d2cf</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10498,22 +10498,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>108.62998</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>CSKA Moscow -1</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x250c9978ebf5b011075be1d4db3f8d11c84ae4775b2a15381141c2041819671d</t>
+          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785572661</t>
+          <t>1785572887</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>136.213141</t>
+          <t>20.464286</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10595,31 +10595,39 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x8287809c6ecbf4350c5b00a693999a7413ec85bf151e6bc30a165f00a63e0841</t>
+          <t>0xdae6a6bc9c468e345de6b0edd818d404c5d319a8b35d8b8e089f27c055c389b5</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>11.39998</t>
+          <t>108.62998</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -10627,27 +10635,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0xd2c373d98f28160b1937cb16fc225505947dd2558aed807adb6793d0ba065168</t>
+          <t>0x250c9978ebf5b011075be1d4db3f8d11c84ae4775b2a15381141c2041819671d</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -10672,17 +10680,17 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785572520</t>
+          <t>1785572661</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>15.971951</t>
+          <t>136.213141</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10699,28 +10707,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x3b18e7fae3a0845fdb30a3cbe728a545cae4e662d0b4f73499445c8c15b3fc40</t>
+          <t>0x8287809c6ecbf4350c5b00a693999a7413ec85bf151e6bc30a165f00a63e0841</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11.39998</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -10731,27 +10739,27 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+          <t>0xd2c373d98f28160b1937cb16fc225505947dd2558aed807adb6793d0ba065168</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -10776,17 +10784,17 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785571166</t>
+          <t>1785572520</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>29.411765</t>
+          <t>15.971951</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10803,28 +10811,28 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x74da0033cbaaf0989652d45e0a379a053226dca51e774fe8f3d59364a7ed7bc3</t>
+          <t>0x3b18e7fae3a0845fdb30a3cbe728a545cae4e662d0b4f73499445c8c15b3fc40</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>21.9974</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -10850,7 +10858,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10880,7 +10888,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785571136</t>
+          <t>1785571166</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10890,7 +10898,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>29.477253</t>
+          <t>29.411765</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10907,7 +10915,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0xdf6e0cf8b56844dd97ec7cd857e88927c45b93f08b350ac9344b7a0606e045b8</t>
+          <t>0x74da0033cbaaf0989652d45e0a379a053226dca51e774fe8f3d59364a7ed7bc3</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10918,7 +10926,7 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>52.31835</t>
+          <t>21.9974</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10984,7 +10992,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785571135</t>
+          <t>1785571136</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10994,7 +11002,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>70.108342</t>
+          <t>29.477253</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -11011,7 +11019,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x018d60ff481049c67bba92e9b54e0d55c42b86a5d701c0b1c584e9807ee17e54</t>
+          <t>0xdf6e0cf8b56844dd97ec7cd857e88927c45b93f08b350ac9344b7a0606e045b8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11022,17 +11030,17 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>14.89036</t>
+          <t>52.31835</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -11058,7 +11066,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -11098,7 +11106,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>87.590353</t>
+          <t>70.108342</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11115,7 +11123,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0xa5cc97a62584698f6c4048c5f24e84a8eadf70fd65b8935042102ef7c64fb9d8</t>
+          <t>0x018d60ff481049c67bba92e9b54e0d55c42b86a5d701c0b1c584e9807ee17e54</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11126,17 +11134,17 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>33.69787</t>
+          <t>14.89036</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.5762</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -11147,27 +11155,27 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0xeb29ac30b54329d5d60f9106332c47c7d06e00b17061f03af8f7e4b413a058ba</t>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -11192,17 +11200,17 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1785571067</t>
+          <t>1785571135</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>58.477866</t>
+          <t>87.590353</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11219,39 +11227,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0xf321b64477a115c8937a87a1a8313c82a213b8e568c8f88293a4375fba41be54</t>
+          <t>0xa5cc97a62584698f6c4048c5f24e84a8eadf70fd65b8935042102ef7c64fb9d8</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>33.69787</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.5762</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Lokomotiv Moscow</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -11259,27 +11259,27 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0x3890375e41e397b7fd55fb869bda99e7fceb1ca0319fe030519bd2ec2cf5bc31</t>
+          <t>0xeb29ac30b54329d5d60f9106332c47c7d06e00b17061f03af8f7e4b413a058ba</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -11304,17 +11304,17 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1785567916</t>
+          <t>1785571067</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>2.233062</t>
+          <t>58.477866</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11331,31 +11331,39 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0xe3ddd7c883204ad1dba275364ab1e46eb717f308b3dedc5acbd7703d980bec00</t>
+          <t>0xf321b64477a115c8937a87a1a8313c82a213b8e568c8f88293a4375fba41be54</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moscow</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -11363,27 +11371,27 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
+          <t>0x3890375e41e397b7fd55fb869bda99e7fceb1ca0319fe030519bd2ec2cf5bc31</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -11408,17 +11416,17 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1785563385</t>
+          <t>1785567916</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>6.700141</t>
+          <t>2.233062</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11435,23 +11443,23 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0xa4c6ae8963dfa3b202fe6ce8ce74f74e1dbf632ba3fc5ac6cee71b986816c930</t>
+          <t>0xe3ddd7c883204ad1dba275364ab1e46eb717f308b3dedc5acbd7703d980bec00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>77.76784</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -11512,7 +11520,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1785563353</t>
+          <t>1785563385</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11522,7 +11530,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>104.737832</t>
+          <t>6.700141</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11539,28 +11547,28 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0x841657eb70bcebb4ab52934f0882d697225406f5e7fd8417bc066ef32cfd9f3f</t>
+          <t>0xa4c6ae8963dfa3b202fe6ce8ce74f74e1dbf632ba3fc5ac6cee71b986816c930</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>77.76784</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -11586,7 +11594,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -11616,7 +11624,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1785563065</t>
+          <t>1785563353</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11626,7 +11634,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>104.737832</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11643,7 +11651,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0xf274d715150d62a93d353cede0f6ff9c88848ac391602271e47187d10e35b365</t>
+          <t>0x841657eb70bcebb4ab52934f0882d697225406f5e7fd8417bc066ef32cfd9f3f</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11654,7 +11662,7 @@
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -11720,7 +11728,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>1785563064</t>
+          <t>1785563065</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -11730,7 +11738,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>2.909091</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11747,7 +11755,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0xf8e15936a562a6c53c3f0b156df3f4beef97db21efe52a96112e59b7b71d2cfc</t>
+          <t>0xf274d715150d62a93d353cede0f6ff9c88848ac391602271e47187d10e35b365</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -11758,7 +11766,7 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -11824,7 +11832,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>1785562017</t>
+          <t>1785563064</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -11834,7 +11842,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>133.527273</t>
+          <t>2.909091</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11851,7 +11859,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0x31383c91bcc01015e13e5fd2b9bea5aca6c5af939719601af5d89e0d14f917d1</t>
+          <t>0xf8e15936a562a6c53c3f0b156df3f4beef97db21efe52a96112e59b7b71d2cfc</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -11862,17 +11870,17 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -11898,7 +11906,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -11928,7 +11936,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>1785561847</t>
+          <t>1785562017</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -11938,7 +11946,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>133.527273</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -11955,7 +11963,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0x62d0c1650da9a9f20785ab148cd57757523f593981c50f9121d975d5671dc22c</t>
+          <t>0x31383c91bcc01015e13e5fd2b9bea5aca6c5af939719601af5d89e0d14f917d1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -11966,17 +11974,17 @@
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -12002,7 +12010,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -12032,7 +12040,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>1785561830</t>
+          <t>1785561847</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -12042,7 +12050,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>34.376812</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -12059,28 +12067,28 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0xca8103b7c29655e3359ce0c76ab74b1e550d22a25b2697a62f009036198b340d</t>
+          <t>0x62d0c1650da9a9f20785ab148cd57757523f593981c50f9121d975d5671dc22c</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -12106,7 +12114,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -12136,7 +12144,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>1785561684</t>
+          <t>1785561830</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -12146,7 +12154,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>29.411765</t>
+          <t>34.376812</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12163,18 +12171,18 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0xd2b6ca67a5a2d819fc0cf69e7b7cb17aef0d37ea042ab1d803ea19a79869cf1c</t>
+          <t>0xca8103b7c29655e3359ce0c76ab74b1e550d22a25b2697a62f009036198b340d</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>15.91241</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -12240,7 +12248,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>1785561659</t>
+          <t>1785561684</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -12250,7 +12258,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>93.602412</t>
+          <t>29.411765</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -12267,28 +12275,28 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0x9df3204fd72e0052ebf44ed8084dee18335fa60165de967589f7ffece734f21d</t>
+          <t>0xd2b6ca67a5a2d819fc0cf69e7b7cb17aef0d37ea042ab1d803ea19a79869cf1c</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0x8AaDb828882f34790D0C35aE0534a6BbDDA6ad19</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15.91241</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -12314,7 +12322,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -12344,7 +12352,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>1785561561</t>
+          <t>1785561659</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -12354,7 +12362,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>21.621622</t>
+          <t>93.602412</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -12371,28 +12379,28 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0x1c651915969f4f1991cb4f8083b94c18de450a29ab1d239f29fd2136f09013cd</t>
+          <t>0x9df3204fd72e0052ebf44ed8084dee18335fa60165de967589f7ffece734f21d</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8AaDb828882f34790D0C35aE0534a6BbDDA6ad19</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>39.53998</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -12403,27 +12411,27 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
+          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -12448,17 +12456,17 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>1785559258</t>
+          <t>1785561561</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>55.39752</t>
+          <t>21.621622</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12475,7 +12483,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0xfe4e061b2e2e2540fd50c22f993ed8e84c7d22f3208b337d5a326d6444353f09</t>
+          <t>0x1c651915969f4f1991cb4f8083b94c18de450a29ab1d239f29fd2136f09013cd</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12486,17 +12494,17 @@
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>97.43997</t>
+          <t>39.53998</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -12522,7 +12530,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>0x5b5b30e2f6739fc9828801a4bc6c1fd66d2d048516210562005b195dab2ed7e8</t>
+          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -12552,7 +12560,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1785559257</t>
+          <t>1785559258</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -12562,7 +12570,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>124.325321</t>
+          <t>55.39752</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -12579,7 +12587,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0x08024130d9cb2665d1fada581c354f0d9912d9be188b8a5b5cd319c76fc8f84b</t>
+          <t>0xfe4e061b2e2e2540fd50c22f993ed8e84c7d22f3208b337d5a326d6444353f09</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12590,17 +12598,17 @@
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0.00083</t>
+          <t>97.43997</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -12626,7 +12634,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
+          <t>0x5b5b30e2f6739fc9828801a4bc6c1fd66d2d048516210562005b195dab2ed7e8</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -12666,7 +12674,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>0.001163</t>
+          <t>124.325321</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -12683,27 +12691,23 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0x7a11de4f80dc40500c7c27e609aa7ce468977e4b318ea22ee056badb255acac0</t>
+          <t>0x08024130d9cb2665d1fada581c354f0d9912d9be188b8a5b5cd319c76fc8f84b</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>0.00083</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1.2775</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -12711,11 +12715,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Dynamo Dagestan Makhachkala</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -12723,27 +12723,27 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
+          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -12768,17 +12768,17 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>1785554288</t>
+          <t>1785559257</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>83.063063</t>
+          <t>0.001163</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -12795,12 +12795,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0x13a6ce7009e637abe73138bc7868471610982f652ed68f38fbb93a4e68405e6c</t>
+          <t>0x7a11de4f80dc40500c7c27e609aa7ce468977e4b318ea22ee056badb255acac0</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>1785552612</t>
+          <t>1785554288</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>18.018018</t>
+          <t>83.063063</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -12907,12 +12907,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0x17588dd455f17e31e06c55e5d5c91052a57c1fc2c2711a0891e74386a507ec57</t>
+          <t>0x13a6ce7009e637abe73138bc7868471610982f652ed68f38fbb93a4e68405e6c</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>1785552583</t>
+          <t>1785552612</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>52.612613</t>
+          <t>18.018018</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -13019,23 +13019,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0x7e4e77fa047e471fb7a25555ab8b596db1c260554e819bf1e556c3fb95efcdad</t>
+          <t>0x17588dd455f17e31e06c55e5d5c91052a57c1fc2c2711a0891e74386a507ec57</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>63.81998</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1.7125</t>
+          <t>1.2775</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -13043,7 +13047,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -13051,27 +13059,27 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
+          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -13096,17 +13104,17 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>1785550426</t>
+          <t>1785552583</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>89.571902</t>
+          <t>52.612613</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -13123,27 +13131,23 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0xe168538382bb9379f973bea17e97bdbec6d33bf8f1675b71dfc9f45ecde2301e</t>
+          <t>0x7e4e77fa047e471fb7a25555ab8b596db1c260554e819bf1e556c3fb95efcdad</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>63.81998</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1.2775</t>
+          <t>1.7125</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -13151,11 +13155,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Dynamo Dagestan Makhachkala</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -13163,27 +13163,27 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
+          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>1785549278</t>
+          <t>1785550426</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>18.018018</t>
+          <t>89.571902</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -13235,12 +13235,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0x01f52f51af10033e9f1c42cddafc3bf0296939cdfd57ee81fc03f9b4ce79db99</t>
+          <t>0xe168538382bb9379f973bea17e97bdbec6d33bf8f1675b71dfc9f45ecde2301e</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>1785549255</t>
+          <t>1785549278</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>57.405405</t>
+          <t>18.018018</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -13347,7 +13347,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0x1638d462ac081048e75f74389a4ff26e18b1ae1b526d3aeb9de1440589cd1e5d</t>
+          <t>0x01f52f51af10033e9f1c42cddafc3bf0296939cdfd57ee81fc03f9b4ce79db99</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13362,22 +13362,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>242.37998</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.2775</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13387,27 +13387,27 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
+          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -13432,17 +13432,17 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>1785522300</t>
+          <t>1785549255</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>336.638861</t>
+          <t>57.405405</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -13459,12 +13459,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0xbb7e9ff01a18bfc8edad554bb31f15afc9af81a591df798303c216a31f4f60a2</t>
+          <t>0x1638d462ac081048e75f74389a4ff26e18b1ae1b526d3aeb9de1440589cd1e5d</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -13474,22 +13474,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>42.87</t>
+          <t>242.37998</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1.3912</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13499,27 +13499,27 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
+          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -13544,17 +13544,17 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>1785519268</t>
+          <t>1785522300</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>109.571885</t>
+          <t>336.638861</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -13571,7 +13571,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0xb20c524d4e546a7083e83d50954cb82e74d2f35919a693305ef85bcd1297f018</t>
+          <t>0xbb7e9ff01a18bfc8edad554bb31f15afc9af81a591df798303c216a31f4f60a2</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13579,15 +13579,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>6.81967</t>
+          <t>42.87</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.3912</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -13595,7 +13599,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -13618,7 +13626,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -13658,7 +13666,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>9.99219</t>
+          <t>109.571885</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -13675,7 +13683,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0x4f0a3bc80edb843b0944d88bf4e31147f77d117de6bec90e861ee3f30e05ab04</t>
+          <t>0xb20c524d4e546a7083e83d50954cb82e74d2f35919a693305ef85bcd1297f018</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13686,17 +13694,17 @@
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>6.81967</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -13722,7 +13730,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -13752,7 +13760,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>1785519266</t>
+          <t>1785519268</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -13762,7 +13770,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>25.18451</t>
+          <t>9.99219</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -13779,18 +13787,18 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0x5ba31b6e54e59ca06de6605e21a3984e6bef3be97c4a38cb1fef0f420c3c5762</t>
+          <t>0x4f0a3bc80edb843b0944d88bf4e31147f77d117de6bec90e861ee3f30e05ab04</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -13856,7 +13864,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>1785517580</t>
+          <t>1785519266</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -13866,7 +13874,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>9.111617</t>
+          <t>25.18451</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -13883,18 +13891,18 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0x34ae51184c54f771408cd03c9262de0e4ea1554f41b9cf4d3f7f2c5d4d746850</t>
+          <t>0x5ba31b6e54e59ca06de6605e21a3984e6bef3be97c4a38cb1fef0f420c3c5762</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>13.93611</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -13960,7 +13968,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>1785517575</t>
+          <t>1785517580</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -13970,7 +13978,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>25.3961</t>
+          <t>9.111617</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -13987,28 +13995,28 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0x7029f30f1995c9929d909d63df9f8e25356451c2543674cd96d9a354775d1cd1</t>
+          <t>0x34ae51184c54f771408cd03c9262de0e4ea1554f41b9cf4d3f7f2c5d4d746850</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>13.93611</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -14019,27 +14027,27 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Rodina Moskva vs Rostov FK</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Rostov FK</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>0x79bda80ec32380a53cc33c980754cff46b3880a7317dd6e783f523b986aea91a</t>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>L19536024</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -14064,17 +14072,17 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>1785513066</t>
+          <t>1785517575</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>1.405961</t>
+          <t>25.3961</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -14091,27 +14099,23 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0xa0c8d19ccd8222fe5808f3173eb4463c8de341ddcfcb086f400632089e4f0be4</t>
+          <t>0x7029f30f1995c9929d909d63df9f8e25356451c2543674cd96d9a354775d1cd1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>50.36</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1.3375</t>
+          <t>1.7113</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14119,11 +14123,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti</t>
-        </is>
-      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -14131,27 +14131,27 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>Rodina Moskva vs Rostov FK</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Rostov FK</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+          <t>0x79bda80ec32380a53cc33c980754cff46b3880a7317dd6e783f523b986aea91a</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536024</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -14176,17 +14176,17 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>1785497556</t>
+          <t>1785513066</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>149.214815</t>
+          <t>1.405961</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -14203,12 +14203,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0x284f0b4a1de283358a3577badffac14ecc5afcfdc28ce21985a9cb86481ba6cc</t>
+          <t>0xa0c8d19ccd8222fe5808f3173eb4463c8de341ddcfcb086f400632089e4f0be4</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0x6d158A0b6c9Df0483460f6a656673630210CAA4a</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14218,22 +14218,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50.36</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.3375</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -14243,27 +14243,27 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Rodina Moskva vs Rostov FK</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Rostov FK</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>0xc2ed80c842ab0c1d24361f465ff9c0b8137d5178739873b6e3325008d77dd204</t>
+          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>L19536024</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -14288,17 +14288,17 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>1785497412</t>
+          <t>1785497556</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>224.089636</t>
+          <t>149.214815</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -14315,31 +14315,39 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0x82023bc913cac320bbcec8856b93c61ced3824bae2ff614f7aeb447196f63721</t>
+          <t>0x284f0b4a1de283358a3577badffac14ecc5afcfdc28ce21985a9cb86481ba6cc</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
+          <t>0x6d158A0b6c9Df0483460f6a656673630210CAA4a</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>139.07045</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1.7913</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -14347,27 +14355,27 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Rodina Moskva vs Rostov FK</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Rostov FK</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+          <t>0xc2ed80c842ab0c1d24361f465ff9c0b8137d5178739873b6e3325008d77dd204</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536024</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -14392,17 +14400,17 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>1785492025</t>
+          <t>1785497412</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>175.760442</t>
+          <t>224.089636</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -14419,7 +14427,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0xb79b0374865c7617b60514b2180feb26aead2aaca0895843000b71787d8212f5</t>
+          <t>0x82023bc913cac320bbcec8856b93c61ced3824bae2ff614f7aeb447196f63721</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -14430,7 +14438,7 @@
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>38.81386</t>
+          <t>139.07045</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -14496,7 +14504,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>1785492024</t>
+          <t>1785492025</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -14506,7 +14514,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>49.053852</t>
+          <t>175.760442</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -14523,110 +14531,214 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>0xb79b0374865c7617b60514b2180feb26aead2aaca0895843000b71787d8212f5</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>38.81386</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1.7913</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>1785492024</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>49.053852</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
           <t>0x35c722e47edc576e91fff2a56006e70c47630baaf10fd0a9c8c7187b33e14e24</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
         <is>
           <t>1.3113</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny vs Spartak Moskva</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="K132" t="inlineStr">
         <is>
           <t>Spartak Moskva</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t>0xba2ac566f21d9b66fba41da0a24a5d93737f4a0c2789de13002227a82662899c</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t>L19537277</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P131" t="inlineStr">
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R131" t="inlineStr">
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
         <is>
           <t>1785344429</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
+      <c r="S132" t="inlineStr">
         <is>
           <t>1785691800</t>
         </is>
       </c>
-      <c r="T131" t="inlineStr">
+      <c r="T132" t="inlineStr">
         <is>
           <t>3.212851</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="U132" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V131" t="inlineStr">
+      <c r="V132" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premier League/trades.xlsx
+++ b/data/sxbet/ligas/Premier League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V136"/>
+  <dimension ref="A1:V137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x792c90ebfb065dc8da54a1d51791c1a7e11d603195573a57532a37feb2930788</t>
+          <t>0xea032a11d8d6683b83c39c09f6ccbffd289a4a3843a81d5495b368385ea418c0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x155C76202e45BE70c50bfeD7eAeA3B98e7716Ff7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>1.60998</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.7412</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Zenit St.Petersburg</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x347ee4906eeef68fdfb5cfd566bd112d8a469ad0d77cdff035feacac03b1279f</t>
+          <t>0xfe528050d181017c1bb058e4608aaa46f0308f1fac83df8cb6378d8983ee39e6</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785617121</t>
+          <t>1785642511</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>8.90625</t>
+          <t>2.17198</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,39 +643,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x650b56117982a480630af2453a0d4f2a4c8d33ee7e50546f03c0c09c926fb221</t>
+          <t>0x792c90ebfb065dc8da54a1d51791c1a7e11d603195573a57532a37feb2930788</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -690,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd7a7817c5bcd556fe1a4f1ada1c843f139b7d3c566d18db6956a20085f803d2f</t>
+          <t>0x347ee4906eeef68fdfb5cfd566bd112d8a469ad0d77cdff035feacac03b1279f</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785616002</t>
+          <t>1785617121</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6.872852</t>
+          <t>8.90625</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x50043f620716e9391ba21bbd0eebdecbc69fcef211b365167c5d2772f819ff1b</t>
+          <t>0x650b56117982a480630af2453a0d4f2a4c8d33ee7e50546f03c0c09c926fb221</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28.54</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785615983</t>
+          <t>1785616002</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>39.230241</t>
+          <t>6.872852</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,31 +859,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xb39613ece8278778fd859432ce085ca95cfe1b8944504f4168781c106fa94fcc</t>
+          <t>0x50043f620716e9391ba21bbd0eebdecbc69fcef211b365167c5d2772f819ff1b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>28.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -891,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>FC Orenburg vs Zenit St.Petersburg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>FC Orenburg</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Zenit St.Petersburg</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf76c63df2e9a35a339fd640182449988ad25e6a6ffbf9ca9c3e57de7cf8ec678</t>
+          <t>0xd7a7817c5bcd556fe1a4f1ada1c843f139b7d3c566d18db6956a20085f803d2f</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536936</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785612049</t>
+          <t>1785615983</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>86.097561</t>
+          <t>39.230241</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,39 +971,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x8c779320e758724f0763d70d66151134fb086c1e1a7a8eaf3324b2d1c7d2f063</t>
+          <t>0xb39613ece8278778fd859432ce085ca95cfe1b8944504f4168781c106fa94fcc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xd2c373d98f28160b1937cb16fc225505947dd2558aed807adb6793d0ba065168</t>
+          <t>0xf76c63df2e9a35a339fd640182449988ad25e6a6ffbf9ca9c3e57de7cf8ec678</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785610673</t>
+          <t>1785612049</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6.10687</t>
+          <t>86.097561</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x50ae7a52a15efcf1c422c41197e194a91af4acb58e614d778935d3d064b16181</t>
+          <t>0x8c779320e758724f0763d70d66151134fb086c1e1a7a8eaf3324b2d1c7d2f063</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1090,22 +1090,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad -0.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xaa9700965af19b33d958192d1e341e976e37028b7fa61b0d892a1b51c842807b</t>
+          <t>0xd2c373d98f28160b1937cb16fc225505947dd2558aed807adb6793d0ba065168</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785606766</t>
+          <t>1785610673</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>14.760148</t>
+          <t>6.10687</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,31 +1187,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x7a432131da1edd8071f1eb7ad6d161c2aa3955629e87b1e9d75eec8c97545a0a</t>
+          <t>0x50ae7a52a15efcf1c422c41197e194a91af4acb58e614d778935d3d064b16181</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>157.62</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad -0.5</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -1234,7 +1242,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
+          <t>0xaa9700965af19b33d958192d1e341e976e37028b7fa61b0d892a1b51c842807b</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785605951</t>
+          <t>1785606766</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>523.219917</t>
+          <t>14.760148</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,28 +1299,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xd0061cc526a8d9b88b00729b269727277b0829533f7989113f37fb4f3a6e354f</t>
+          <t>0x7a432131da1edd8071f1eb7ad6d161c2aa3955629e87b1e9d75eec8c97545a0a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18.77999</t>
+          <t>157.62</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1338,7 +1346,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xe8207537e82b7cc6c2d40b1ffb94fb6a1298e8ffae224ad112dd145d2479d140</t>
+          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785605002</t>
+          <t>1785605951</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>29.63312</t>
+          <t>523.219917</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xed19f145677d00a1f377e327de7701c987d2a801382c985554f3b5246d4f7574</t>
+          <t>0xd0061cc526a8d9b88b00729b269727277b0829533f7989113f37fb4f3a6e354f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1403,19 +1411,15 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>18.77999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.6338</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1423,26 +1427,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>FC Baltika Kaliningrad</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Dynamo Moscow</t>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x2634a9ad4709864d52fc8aa66fba0d772c164035502c70501d9eec4578d50acc</t>
+          <t>0xe8207537e82b7cc6c2d40b1ffb94fb6a1298e8ffae224ad112dd145d2479d140</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785604611</t>
+          <t>1785605002</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>154.646617</t>
+          <t>29.63312</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xfc054e64f38b9eb4b1b012b19f4f9aa56fd4806dd6173dd23f29cb17367aa31d</t>
+          <t>0xed19f145677d00a1f377e327de7701c987d2a801382c985554f3b5246d4f7574</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>51.42</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7563</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1547,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
+          <t>0x2634a9ad4709864d52fc8aa66fba0d772c164035502c70501d9eec4578d50acc</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785604104</t>
+          <t>1785604611</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>6.61157</t>
+          <t>154.646617</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xf05f75588bcd4ac061fc839cdafce4772aae26056ae40d8c6134f8592718fb9e</t>
+          <t>0xfc054e64f38b9eb4b1b012b19f4f9aa56fd4806dd6173dd23f29cb17367aa31d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>387.31856</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.7563</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x9125ce6f5ed52866b9368acc8e59eaffa5f02b8d5d4cd6bde41a6a1aaf05c16a</t>
+          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785603814</t>
+          <t>1785604104</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1526.378562</t>
+          <t>6.61157</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,12 +1731,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xbc831519a8d27b040d43b5495628a8039bdd1bb9deed0b72e68bbec6ab394032</t>
+          <t>0xf05f75588bcd4ac061fc839cdafce4772aae26056ae40d8c6134f8592718fb9e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1746,22 +1746,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.19999</t>
+          <t>387.31856</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xa99b14a45dd025e0d0b51f2a7021a6ce34c45565608d4ed6a189bdd8dfee08d3</t>
+          <t>0x9125ce6f5ed52866b9368acc8e59eaffa5f02b8d5d4cd6bde41a6a1aaf05c16a</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785603674</t>
+          <t>1785603814</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5.844731</t>
+          <t>1526.378562</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,31 +1843,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x2279e851617cc78ef830ec1d05fd54bbdd2b673d8932991cfbb4cf20008040c8</t>
+          <t>0xbc831519a8d27b040d43b5495628a8039bdd1bb9deed0b72e68bbec6ab394032</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>3.19999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -1890,7 +1898,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x84855b76b3233b3863b628dae07980f03631d882c2ff3527cb6d8157953600b2</t>
+          <t>0xa99b14a45dd025e0d0b51f2a7021a6ce34c45565608d4ed6a189bdd8dfee08d3</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1920,7 +1928,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785603599</t>
+          <t>1785603674</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1930,7 +1938,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>76.469274</t>
+          <t>5.844731</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,39 +1955,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x22a61f4e6ccd6958df2fbd2e12f0b0760e9ecc0c9b8ad8f529059ae7deaa5605</t>
+          <t>0x2279e851617cc78ef830ec1d05fd54bbdd2b673d8932991cfbb4cf20008040c8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.7188</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -1987,27 +1987,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
+          <t>0x84855b76b3233b3863b628dae07980f03631d882c2ff3527cb6d8157953600b2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785600110</t>
+          <t>1785603599</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>6.956522</t>
+          <t>76.469274</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xc38ef3f3b6d17f49fde86d0c249d5198de659a285ba5e66f9e5d30702b1539ad</t>
+          <t>0x22a61f4e6ccd6958df2fbd2e12f0b0760e9ecc0c9b8ad8f529059ae7deaa5605</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>151.58</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785600100</t>
+          <t>1785600110</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>210.893913</t>
+          <t>6.956522</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,31 +2171,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x0ac02cd68cef7f84b9d5edb2b42052b1581ab555504ea9eb7599dc3881e3ae7a</t>
+          <t>0xc38ef3f3b6d17f49fde86d0c249d5198de659a285ba5e66f9e5d30702b1539ad</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>14.82999</t>
+          <t>151.58</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.6475</t>
+          <t>1.7188</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -2203,27 +2211,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x48039cdeb89ebeb5a381396af9889bb029cca38a9035853205d890164d76b1e6</t>
+          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2248,17 +2256,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785597306</t>
+          <t>1785600100</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>22.903459</t>
+          <t>210.893913</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,28 +2283,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x6d5b2bcf883aa8f56cc1543e99253fb8badd13a550153724bea18a68328b3edc</t>
+          <t>0x0ac02cd68cef7f84b9d5edb2b42052b1581ab555504ea9eb7599dc3881e3ae7a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14.82999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.8788</t>
+          <t>1.6475</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2322,7 +2330,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x4ebbf978346ce1ea467975cc8563aeb19503b54fbc259dee4316cf0b7c0b5070</t>
+          <t>0x48039cdeb89ebeb5a381396af9889bb029cca38a9035853205d890164d76b1e6</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2352,7 +2360,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785597145</t>
+          <t>1785597306</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2362,7 +2370,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>5.6899</t>
+          <t>22.903459</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2379,18 +2387,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x127fe57658e163511b1474b93d7cf756021956ac9bca4584ad6af7c64077836d</t>
+          <t>0x6d5b2bcf883aa8f56cc1543e99253fb8badd13a550153724bea18a68328b3edc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>14.63973</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2456,7 +2464,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785597104</t>
+          <t>1785597145</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2466,7 +2474,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>16.659721</t>
+          <t>5.6899</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2483,18 +2491,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x8025258561a6773ef950e12d7e2d5512dc21ca44c1b37a63b7e1125f3c80a7c4</t>
+          <t>0x127fe57658e163511b1474b93d7cf756021956ac9bca4584ad6af7c64077836d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14.63973</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2560,7 +2568,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785596844</t>
+          <t>1785597104</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2570,7 +2578,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>5.6899</t>
+          <t>16.659721</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2587,18 +2595,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x78f2cf0c44a1f9226c252b915c49a139e2cabfde0061a719e26c996fa1bbbeac</t>
+          <t>0x8025258561a6773ef950e12d7e2d5512dc21ca44c1b37a63b7e1125f3c80a7c4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>213.36406</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2664,7 +2672,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785596828</t>
+          <t>1785596844</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2674,7 +2682,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>242.804051</t>
+          <t>5.6899</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2691,39 +2699,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x5c792d7ccdce5d1dcc92bb439a1c386db3cdc678bf74f30175c5605f1bcee1c6</t>
+          <t>0x78f2cf0c44a1f9226c252b915c49a139e2cabfde0061a719e26c996fa1bbbeac</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>110.26999</t>
+          <t>213.36406</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Dynamo Dagestan Makhachkala +1</t>
-        </is>
-      </c>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xae5fbc672993d49fa7942061b539cb2fc8ebf0617f93d35cbeb337ad8744dea1</t>
+          <t>0x4ebbf978346ce1ea467975cc8563aeb19503b54fbc259dee4316cf0b7c0b5070</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785596769</t>
+          <t>1785596828</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>151.31388</t>
+          <t>242.804051</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2803,31 +2803,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x770475a22a747562c30442cf508e4c41e1186276aa0f531ce19cdaa7665217c7</t>
+          <t>0x5c792d7ccdce5d1dcc92bb439a1c386db3cdc678bf74f30175c5605f1bcee1c6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x869E0d5a56DC19f2A97743B65A2CD60b8470152F</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>110.26999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala +1</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -2835,27 +2843,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+          <t>0xae5fbc672993d49fa7942061b539cb2fc8ebf0617f93d35cbeb337ad8744dea1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2880,17 +2888,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785595958</t>
+          <t>1785596769</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>19.230769</t>
+          <t>151.31388</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2907,39 +2915,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x235bda23b440cf84c9236798e7a0fbf2c45cee263fbece7f20c160066960939e</t>
+          <t>0x770475a22a747562c30442cf508e4c41e1186276aa0f531ce19cdaa7665217c7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x869E0d5a56DC19f2A97743B65A2CD60b8470152F</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>25.34</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xd87e3e74d56c50a95f7eeab8f4e9093ec05b11e3354fb707ffcb563eeb3c5ea4</t>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785595503</t>
+          <t>1785595958</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>422.333333</t>
+          <t>19.230769</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3019,7 +3019,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xa81148619186b65d428a0ab1d5db583edc7e6abb8ec4b50e95b4141c37af730d</t>
+          <t>0x235bda23b440cf84c9236798e7a0fbf2c45cee263fbece7f20c160066960939e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>25.34</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785595501</t>
+          <t>1785595503</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>422.333333</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3131,7 +3131,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x4311b0c91c1e0cca14112e39dc165fb2a99f6a11ca9a89047e34ad1cb640d6b3</t>
+          <t>0xa81148619186b65d428a0ab1d5db583edc7e6abb8ec4b50e95b4141c37af730d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785595499</t>
+          <t>1785595501</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>435.166667</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x95636b08910b61970464a5fb5bb180432ebfb98e38177a7ebcca4a09b973ed40</t>
+          <t>0x4311b0c91c1e0cca14112e39dc165fb2a99f6a11ca9a89047e34ad1cb640d6b3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8b0c1cadD582567253C6e5F04361F059619f2f06</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3258,22 +3258,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3925</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0xd87e3e74d56c50a95f7eeab8f4e9093ec05b11e3354fb707ffcb563eeb3c5ea4</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785595382</t>
+          <t>1785595499</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2.547771</t>
+          <t>435.166667</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3355,12 +3355,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x7d6d6d79ceff309c95f350345d24a4a049f0469132844a7e672d7642aa2fbb26</t>
+          <t>0x95636b08910b61970464a5fb5bb180432ebfb98e38177a7ebcca4a09b973ed40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x8b0c1cadD582567253C6e5F04361F059619f2f06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3370,22 +3370,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>105.38</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.3925</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785595337</t>
+          <t>1785595382</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1453.517241</t>
+          <t>2.547771</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3467,12 +3467,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x74f88bd94a20141b2f689fbc9ee79cf2ad4ac87d15231b684850e3599184da52</t>
+          <t>0x7d6d6d79ceff309c95f350345d24a4a049f0469132844a7e672d7642aa2fbb26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x814d79A9940CbC5Af4C19cAa118EC065a77CD31f</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3482,39 +3482,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>105.38</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4312</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>CSKA Moscow</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>CSKA Moscow</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Krylia Sovetov</t>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785595294</t>
+          <t>1785595337</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>18.550725</t>
+          <t>1453.517241</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3579,12 +3579,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xea47e5e3f4d871a56d5cc47a9c4a1ac2fef6617d5149bed973c0c27e341338d9</t>
+          <t>0x74f88bd94a20141b2f689fbc9ee79cf2ad4ac87d15231b684850e3599184da52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x814d79A9940CbC5Af4C19cAa118EC065a77CD31f</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3594,22 +3594,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>181.67908</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.1187</t>
+          <t>1.4312</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785594965</t>
+          <t>1785595294</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1529.929095</t>
+          <t>18.550725</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3691,12 +3691,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xbf4661a11f952621b4227333cad433ff5cf2c3675620b42b2ccc13e871dc27a0</t>
+          <t>0xea47e5e3f4d871a56d5cc47a9c4a1ac2fef6617d5149bed973c0c27e341338d9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8b0c1cadD582567253C6e5F04361F059619f2f06</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3706,22 +3706,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>181.67908</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.1187</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x7f8975f5bd29ad9963300500e7270929609de63bb399f3d8760b7e6131ddcf98</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785594922</t>
+          <t>1785594965</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.985112</t>
+          <t>1529.929095</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3803,12 +3803,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x1c5226d2320fb26e307a8eb3ec872719f375af1337b3c17f6684cf399e639635</t>
+          <t>0xbf4661a11f952621b4227333cad433ff5cf2c3675620b42b2ccc13e871dc27a0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8b0c1cadD582567253C6e5F04361F059619f2f06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3818,22 +3818,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.7188</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3843,27 +3843,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
+          <t>0x7f8975f5bd29ad9963300500e7270929609de63bb399f3d8760b7e6131ddcf98</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3888,17 +3888,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785594048</t>
+          <t>1785594922</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>6.956522</t>
+          <t>1.985112</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3915,12 +3915,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x4c9cc9ccaed8c6a6c550ae2f4e3650e53a05908358942c69cad0831163b816a1</t>
+          <t>0x1c5226d2320fb26e307a8eb3ec872719f375af1337b3c17f6684cf399e639635</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785594029</t>
+          <t>1785594048</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>62.358261</t>
+          <t>6.956522</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4027,7 +4027,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xd41ffcf00a30cf05017e50b4fafa0af98ebf4cb2c973b0c7b07694d0d3176f23</t>
+          <t>0x4c9cc9ccaed8c6a6c550ae2f4e3650e53a05908358942c69cad0831163b816a1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4042,22 +4042,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>307.43999</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.7188</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4067,27 +4067,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xd1cf347863a77aa700b93801eb228f9123026b23f36d67a3b0ffd65a9abe81c0</t>
+          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4112,17 +4112,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785593346</t>
+          <t>1785594029</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>492.889764</t>
+          <t>62.358261</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4139,7 +4139,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x7f2c88e28d01d35404ba595fce0e3b09c96ec24de31112619729efb09352b57b</t>
+          <t>0xd41ffcf00a30cf05017e50b4fafa0af98ebf4cb2c973b0c7b07694d0d3176f23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4154,22 +4154,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>34.89999</t>
+          <t>307.43999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.7212</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x51e9cf87343115ee189ed1aba6feb100a49e6885fd6d113601d07829abebf384</t>
+          <t>0xd1cf347863a77aa700b93801eb228f9123026b23f36d67a3b0ffd65a9abe81c0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>48.388201</t>
+          <t>492.889764</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4251,31 +4251,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xf64924be42de3b43b03c8cff95357c3d85934d1dadd99c0151718a6c68c622f3</t>
+          <t>0x7f2c88e28d01d35404ba595fce0e3b09c96ec24de31112619729efb09352b57b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xCA5FE59CB511e3B15948861b939f0CA0BC22f990</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>34.89999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.7212</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -4283,27 +4291,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0x51e9cf87343115ee189ed1aba6feb100a49e6885fd6d113601d07829abebf384</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4328,17 +4336,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785592840</t>
+          <t>1785593346</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.649485</t>
+          <t>48.388201</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4355,39 +4363,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xc95d3e9241a8ab5ab7b7dcf5d2a951b0d9f4d9707cccf2a8e6cd1ea1d80d2439</t>
+          <t>0xf64924be42de3b43b03c8cff95357c3d85934d1dadd99c0151718a6c68c622f3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xCA5FE59CB511e3B15948861b939f0CA0BC22f990</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15.10999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -4395,27 +4395,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xd1cf347863a77aa700b93801eb228f9123026b23f36d67a3b0ffd65a9abe81c0</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4440,17 +4440,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785592835</t>
+          <t>1785592840</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>24.370952</t>
+          <t>1.649485</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4467,31 +4467,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xf8e021489ea1c7b0226fe5f713cd39f5736596eb8671400efbca9c4d5c8cb41a</t>
+          <t>0xc95d3e9241a8ab5ab7b7dcf5d2a951b0d9f4d9707cccf2a8e6cd1ea1d80d2439</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xCA5FE59CB511e3B15948861b939f0CA0BC22f990</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.10999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.6075</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -4499,27 +4507,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0xd1cf347863a77aa700b93801eb228f9123026b23f36d67a3b0ffd65a9abe81c0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4544,17 +4552,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785592813</t>
+          <t>1785592835</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1.646091</t>
+          <t>24.370952</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4571,39 +4579,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xc96fbe1aca4911173d2e73d29d24e82082f72c91fb2d9d22198f4e17b0daa7cc</t>
+          <t>0xf8e021489ea1c7b0226fe5f713cd39f5736596eb8671400efbca9c4d5c8cb41a</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xCA5FE59CB511e3B15948861b939f0CA0BC22f990</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>29.58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.8137</t>
+          <t>1.6075</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>CSKA Moscow -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x2412409c0dd32a8d9afa2868789771e8bd2fbb4ff00df2699b025196a4208fe6</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785592455</t>
+          <t>1785592813</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>36.35023</t>
+          <t>1.646091</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4683,7 +4683,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xb0d4d9e860a08d8a292bf7157c7e210af4e07fdd308da88048d016afd3a255e4</t>
+          <t>0xc96fbe1aca4911173d2e73d29d24e82082f72c91fb2d9d22198f4e17b0daa7cc</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4708,29 +4708,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>CSKA Moscow -0.5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>CSKA Moscow</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>CSKA Moscow</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Krylia Sovetov</t>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+          <t>0x2412409c0dd32a8d9afa2868789771e8bd2fbb4ff00df2699b025196a4208fe6</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x83dc737ceb377e4b5b06cf4bec789a04964df61c68c148f31504279914da6ba2</t>
+          <t>0xb0d4d9e860a08d8a292bf7157c7e210af4e07fdd308da88048d016afd3a255e4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4810,22 +4810,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>37.34998</t>
+          <t>29.58</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.7412</t>
+          <t>1.8137</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CSKA Moscow -1</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785592440</t>
+          <t>1785592455</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>50.387831</t>
+          <t>36.35023</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x3bcc92e2ec706f2ceb301ed4c824be2e3e926245e15a2e493daf383993605e7a</t>
+          <t>0x83dc737ceb377e4b5b06cf4bec789a04964df61c68c148f31504279914da6ba2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>212.54</t>
+          <t>37.34998</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785592417</t>
+          <t>1785592440</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>286.731872</t>
+          <t>50.387831</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5019,7 +5019,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xbba29fda9dedca632ac108d9a69d5a0c157e4e8061cce4257f8b8ce4d3b67f56</t>
+          <t>0x3bcc92e2ec706f2ceb301ed4c824be2e3e926245e15a2e493daf383993605e7a</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>136.35998</t>
+          <t>212.54</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785592408</t>
+          <t>1785592417</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>183.959501</t>
+          <t>286.731872</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5131,7 +5131,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x224ceaf34c69289e46cb33799c850a0aa119d1a3452f13001574ce16f9ab1e63</t>
+          <t>0xbba29fda9dedca632ac108d9a69d5a0c157e4e8061cce4257f8b8ce4d3b67f56</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5146,22 +5146,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>380.27565</t>
+          <t>136.35998</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.7412</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>CSKA Moscow -1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
+          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785592215</t>
+          <t>1785592408</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1728.525682</t>
+          <t>183.959501</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5243,7 +5243,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x487dc2b53bf8a100c2e3feb8bcb6a3d3a333ca75dabd3839c7910dfaa2e6bd23</t>
+          <t>0x224ceaf34c69289e46cb33799c850a0aa119d1a3452f13001574ce16f9ab1e63</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>149.43</t>
+          <t>380.27565</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785592193</t>
+          <t>1785592215</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>679.227273</t>
+          <t>1728.525682</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5355,7 +5355,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x1a77166bd82bda7e2b3f101a4630482c49539e60be95942f73b6c4975e472114</t>
+          <t>0x487dc2b53bf8a100c2e3feb8bcb6a3d3a333ca75dabd3839c7910dfaa2e6bd23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>385.83</t>
+          <t>149.43</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785592178</t>
+          <t>1785592193</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1734.067416</t>
+          <t>679.227273</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5467,7 +5467,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xe09ad43dd9944457aceae37ee59366c61bbac0d396f68771268284bd5c87d0c0</t>
+          <t>0x1a77166bd82bda7e2b3f101a4630482c49539e60be95942f73b6c4975e472114</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5482,22 +5482,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>387.25</t>
+          <t>385.83</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
+          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785592174</t>
+          <t>1785592178</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1015.737705</t>
+          <t>1734.067416</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5579,31 +5579,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xf88c88a29be02fb94a9dab0fbc4e2ed0bac224f88e9b4b779477e1490042e2ae</t>
+          <t>0xe09ad43dd9944457aceae37ee59366c61bbac0d396f68771268284bd5c87d0c0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.03999</t>
+          <t>387.25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5813</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -5626,7 +5634,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x8ffd92622adb93bd2101fc238161617dbb8897d09ee6afc55f29307cb3793d05</t>
+          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5656,7 +5664,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785591692</t>
+          <t>1785592174</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5666,7 +5674,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1.78923</t>
+          <t>1015.737705</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5683,28 +5691,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x1ee1488fc31a3a0e48b798b5ac1dd5ecfb00e524f3206d2450e438d416d9c193</t>
+          <t>0xf88c88a29be02fb94a9dab0fbc4e2ed0bac224f88e9b4b779477e1490042e2ae</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>520.52997</t>
+          <t>1.03999</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.8825</t>
+          <t>1.5813</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5730,7 +5738,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x4141b7262e76b825e847b7193427b95d711fe2bb2c28b855bd078338d783a1b1</t>
+          <t>0x8ffd92622adb93bd2101fc238161617dbb8897d09ee6afc55f29307cb3793d05</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5760,7 +5768,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785590379</t>
+          <t>1785591692</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5770,7 +5778,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>589.83566</t>
+          <t>1.78923</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5787,7 +5795,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xe6e5db04c3d252eec750387fc6b8ce1112a01b303faef17214a4fd1beb91207d</t>
+          <t>0x1ee1488fc31a3a0e48b798b5ac1dd5ecfb00e524f3206d2450e438d416d9c193</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5798,12 +5806,12 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>520.52997</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.8825</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5819,27 +5827,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xa99b14a45dd025e0d0b51f2a7021a6ce34c45565608d4ed6a189bdd8dfee08d3</t>
+          <t>0x4141b7262e76b825e847b7193427b95d711fe2bb2c28b855bd078338d783a1b1</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5864,17 +5872,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785590151</t>
+          <t>1785590379</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>36.986111</t>
+          <t>589.83566</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5891,27 +5899,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x965a0a328480fa4a41790b4f7637b6a583f61eb86a2b8ed0fc0f9870bc65f420</t>
+          <t>0xe6e5db04c3d252eec750387fc6b8ce1112a01b303faef17214a4fd1beb91207d</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.2063</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5919,11 +5923,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -5931,27 +5931,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+          <t>0xa99b14a45dd025e0d0b51f2a7021a6ce34c45565608d4ed6a189bdd8dfee08d3</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5976,17 +5976,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785589316</t>
+          <t>1785590151</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>73.018182</t>
+          <t>36.986111</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6003,12 +6003,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x28afed33e94a59282b8d2c84464b244379f7d6408ba99eebcdfafd995420f4bd</t>
+          <t>0x965a0a328480fa4a41790b4f7637b6a583f61eb86a2b8ed0fc0f9870bc65f420</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6018,39 +6018,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>60.47996</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.8325</t>
+          <t>1.2063</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>CSKA Moscow</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>CSKA Moscow</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>Krylia Sovetov</t>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785588862</t>
+          <t>1785589316</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>72.648601</t>
+          <t>73.018182</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6115,31 +6115,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x60a2233a146993b8ac9fe21ae7d844b4dad360e92a15e78203e2cc6e0d5cc4a1</t>
+          <t>0x28afed33e94a59282b8d2c84464b244379f7d6408ba99eebcdfafd995420f4bd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>60.47996</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.7388</t>
+          <t>1.8325</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -6162,7 +6170,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6192,7 +6200,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785587961</t>
+          <t>1785588862</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6202,7 +6210,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>6.768162</t>
+          <t>72.648601</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6219,18 +6227,18 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x9c46c5a0d8c22ad2368bb391449ddf09edaa96170ccb65a1f3ca65b25097b289</t>
+          <t>0x60a2233a146993b8ac9fe21ae7d844b4dad360e92a15e78203e2cc6e0d5cc4a1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>103.91983</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6296,7 +6304,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785587946</t>
+          <t>1785587961</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6306,7 +6314,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>140.669821</t>
+          <t>6.768162</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6323,54 +6331,46 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x18458bdae26217c9a02527ebde2e8fdfd56ad86d5959ef901d301f7f162955b6</t>
+          <t>0x9c46c5a0d8c22ad2368bb391449ddf09edaa96170ccb65a1f3ca65b25097b289</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x8FFa640b1a609341C606048226D609Caa3D8F534</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>103.91983</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.7388</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>CSKA Moscow</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>CSKA Moscow</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>Krylia Sovetov</t>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785587168</t>
+          <t>1785587946</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>32.59854</t>
+          <t>140.669821</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6435,31 +6435,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xd05d88b9fc84bf4104af718f1f40a9323b34ac84cf741c06ddc9f34886848b5e</t>
+          <t>0x18458bdae26217c9a02527ebde2e8fdfd56ad86d5959ef901d301f7f162955b6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0x8FFa640b1a609341C606048226D609Caa3D8F534</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>505.16901</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -6467,27 +6475,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xa33f025604fd2a2fc54933008b6c278b1d57959363cf2c1babb844c699caed0d</t>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6512,17 +6520,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785585935</t>
+          <t>1785587168</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>908.169007</t>
+          <t>32.59854</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6539,7 +6547,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xc5a381716ff4466fb74dd190e49d7675fbb8f26575dc66b9cd0f6bc083bbbf12</t>
+          <t>0xd05d88b9fc84bf4104af718f1f40a9323b34ac84cf741c06ddc9f34886848b5e</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6547,31 +6555,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>73.65</t>
+          <t>505.16901</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (6)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Over 6.0</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x584e346bab3cebc0c715fcf0640eb5290a5c0a96732e7e83570bd97ebba5d395</t>
+          <t>0xa33f025604fd2a2fc54933008b6c278b1d57959363cf2c1babb844c699caed0d</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785585070</t>
+          <t>1785585935</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1202.44898</t>
+          <t>908.169007</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6651,7 +6651,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x3d35c451671ff9eb43b21ae0b250eb75eee54546feaa62a1ca9b78b7fd6e0d27</t>
+          <t>0xc5a381716ff4466fb74dd190e49d7675fbb8f26575dc66b9cd0f6bc083bbbf12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>71.53</t>
+          <t>73.65</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785585067</t>
+          <t>1785585070</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1167.836735</t>
+          <t>1202.44898</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6763,31 +6763,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x8940dac2686c289f7c861dabf9fc00df95ca01be5b3ea13c3485603a628c17df</t>
+          <t>0x3d35c451671ff9eb43b21ae0b250eb75eee54546feaa62a1ca9b78b7fd6e0d27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>71.53</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>Under/Over (6)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Over 6.0</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -6795,27 +6803,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x3890375e41e397b7fd55fb869bda99e7fceb1ca0319fe030519bd2ec2cf5bc31</t>
+          <t>0x584e346bab3cebc0c715fcf0640eb5290a5c0a96732e7e83570bd97ebba5d395</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6840,17 +6848,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785583664</t>
+          <t>1785585067</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1.855856</t>
+          <t>1167.836735</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6867,39 +6875,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xec27e0788abf17d968f42b04eafa023a6eba129883cb1e3876be9d378a83e751</t>
+          <t>0x8940dac2686c289f7c861dabf9fc00df95ca01be5b3ea13c3485603a628c17df</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3Cd99B8d9ff9F970d873FD51Db34a241440516</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.6587</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -6907,27 +6907,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xeb29ac30b54329d5d60f9106332c47c7d06e00b17061f03af8f7e4b413a058ba</t>
+          <t>0x3890375e41e397b7fd55fb869bda99e7fceb1ca0319fe030519bd2ec2cf5bc31</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6952,17 +6952,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785583182</t>
+          <t>1785583664</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>12.144213</t>
+          <t>1.855856</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6979,12 +6979,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xb1960c7a23b3de34f30b49e815403305310b24201207e590f7ca2d78675dc84a</t>
+          <t>0xec27e0788abf17d968f42b04eafa023a6eba129883cb1e3876be9d378a83e751</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3Cd99B8d9ff9F970d873FD51Db34a241440516</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6994,22 +6994,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>104.68</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.6587</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x38e80927c0a6c6a6cc0e5fe3192052f0eca332106c22fed66bbabfe0bc9639ef</t>
+          <t>0xeb29ac30b54329d5d60f9106332c47c7d06e00b17061f03af8f7e4b413a058ba</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785581549</t>
+          <t>1785583182</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>178.940171</t>
+          <t>12.144213</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7091,31 +7091,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x35b45074731811f6a18d4f27b8e6bc36b2b4a7c5d4806c8dd65290c77c9c37cd</t>
+          <t>0xb1960c7a23b3de34f30b49e815403305310b24201207e590f7ca2d78675dc84a</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20.85187</t>
+          <t>104.68</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.2363</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -7138,7 +7146,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x601087387a28c77812b112d8474717401c18647e54d4756ab3fdba097f85ec37</t>
+          <t>0x38e80927c0a6c6a6cc0e5fe3192052f0eca332106c22fed66bbabfe0bc9639ef</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7168,7 +7176,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785581132</t>
+          <t>1785581549</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7178,7 +7186,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>88.261884</t>
+          <t>178.940171</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7195,28 +7203,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xfa50a9ed43bd66076a555f0ac40fc5b1a211bafe0d1b6da263a6b8eba4bcdf0e</t>
+          <t>0x35b45074731811f6a18d4f27b8e6bc36b2b4a7c5d4806c8dd65290c77c9c37cd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>20.85187</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.2363</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -7242,7 +7250,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
+          <t>0x601087387a28c77812b112d8474717401c18647e54d4756ab3fdba097f85ec37</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7272,7 +7280,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785580982</t>
+          <t>1785581132</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7282,7 +7290,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>4.721541</t>
+          <t>88.261884</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7299,23 +7307,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xb523260d447b81e1b44693f689118d4542dde7579c64b2178af4a1ea620d7f2f</t>
+          <t>0xfa50a9ed43bd66076a555f0ac40fc5b1a211bafe0d1b6da263a6b8eba4bcdf0e</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7346,7 +7354,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
+          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7376,7 +7384,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785580513</t>
+          <t>1785580982</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7386,7 +7394,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>8.281573</t>
+          <t>4.721541</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7403,39 +7411,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xcc85f1682b7ccf4520cfb9a48b5664a79d5fdf8a5e44b6159877d3dbea266eb7</t>
+          <t>0xb523260d447b81e1b44693f689118d4542dde7579c64b2178af4a1ea620d7f2f</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>235.54997</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti +1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x601087387a28c77812b112d8474717401c18647e54d4756ab3fdba097f85ec37</t>
+          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785580491</t>
+          <t>1785580513</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>302.958161</t>
+          <t>8.281573</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7515,7 +7515,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x21084d8b56382ab72d2397bc760b32e74b434d258e1a7b26a8d608ca837c7bf5</t>
+          <t>0xcc85f1682b7ccf4520cfb9a48b5664a79d5fdf8a5e44b6159877d3dbea266eb7</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7523,23 +7523,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>214.19601</t>
+          <t>235.54997</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti +1</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -7562,7 +7570,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
+          <t>0x601087387a28c77812b112d8474717401c18647e54d4756ab3fdba097f85ec37</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7602,7 +7610,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>354.776</t>
+          <t>302.958161</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7619,7 +7627,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x0f1ec682294b81b957ec9320ab2ba03a785eb144eaa7015bc6aa0c7d36dc9784</t>
+          <t>0x21084d8b56382ab72d2397bc760b32e74b434d258e1a7b26a8d608ca837c7bf5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7627,19 +7635,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>60.29469</t>
+          <t>214.19601</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.3062</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7647,26 +7651,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>Akron Tolyatti</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>Rubin Kazan</t>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785580474</t>
+          <t>1785580491</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>196.88062</t>
+          <t>354.776</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7731,12 +7731,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xacb367c0fc88d2c85ecb600f69dd10c67b60f8988daff7659225967aa379d176</t>
+          <t>0x0f1ec682294b81b957ec9320ab2ba03a785eb144eaa7015bc6aa0c7d36dc9784</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60.29469</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785580472</t>
+          <t>1785580474</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>16.326531</t>
+          <t>196.88062</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7843,12 +7843,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xe3a1a841a351bcdd8a484cd64114f2d7db1dfd75800cd3ee134233667db90ea6</t>
+          <t>0xacb367c0fc88d2c85ecb600f69dd10c67b60f8988daff7659225967aa379d176</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785580471</t>
+          <t>1785580472</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>16.326531</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7955,7 +7955,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x45804ff4b428c2108aa52a14a28a1f369431ae728197068028893a8af476a7b4</t>
+          <t>0xe3a1a841a351bcdd8a484cd64114f2d7db1dfd75800cd3ee134233667db90ea6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785580441</t>
+          <t>1785580471</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>121.077551</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8067,7 +8067,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x0eb822189e746c5e95fe5853d2f4fc74971bb537879255ad9d205c8196d1a2eb</t>
+          <t>0x45804ff4b428c2108aa52a14a28a1f369431ae728197068028893a8af476a7b4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8082,22 +8082,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.4325</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Akron Tolyatti 0</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785580440</t>
+          <t>1785580441</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>118.774566</t>
+          <t>121.077551</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8179,12 +8179,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x2fab84ac790d16a69c18a7a9dd47379a135901c31ac1a4f1c3d6f7d3e92d3854</t>
+          <t>0x0eb822189e746c5e95fe5853d2f4fc74971bb537879255ad9d205c8196d1a2eb</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4325</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8209,24 +8209,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>Akron Tolyatti 0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t>Akron Tolyatti</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>Rubin Kazan</t>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x19c474e600655dfbc3f44466abb293af14cd945496e841a711a52e75c96885db</t>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785580316</t>
+          <t>1785580440</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>11.627907</t>
+          <t>118.774566</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8291,7 +8291,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x70719f041d0bf5efce4a5ba7bfcad8d865f58d1176e9059a57d39a090e9cf2ba</t>
+          <t>0x2fab84ac790d16a69c18a7a9dd47379a135901c31ac1a4f1c3d6f7d3e92d3854</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785580314</t>
+          <t>1785580316</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xf591bb29dd4b46408f825e48edd0794dabb3d8fd69d8f446eb6d3902650c3b78</t>
+          <t>0x70719f041d0bf5efce4a5ba7bfcad8d865f58d1176e9059a57d39a090e9cf2ba</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785580312</t>
+          <t>1785580314</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8515,7 +8515,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x39ad701757f1d9ca28f9d14e317c6b9eeea74c3a6e4a465fb14c21a36372b243</t>
+          <t>0xf591bb29dd4b46408f825e48edd0794dabb3d8fd69d8f446eb6d3902650c3b78</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785580310</t>
+          <t>1785580312</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8627,12 +8627,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x036248e84feca2cdfc6fb53e4bc061d3eefed42a0092f926e8a1746b7a894a56</t>
+          <t>0x39ad701757f1d9ca28f9d14e317c6b9eeea74c3a6e4a465fb14c21a36372b243</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785580306</t>
+          <t>1785580310</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>33.651163</t>
+          <t>11.627907</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8739,7 +8739,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x1e50f9baf79081d66608d3a7ab5b5a987a6af5077945ef59e02797b63779d25e</t>
+          <t>0x036248e84feca2cdfc6fb53e4bc061d3eefed42a0092f926e8a1746b7a894a56</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785580305</t>
+          <t>1785580306</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>162.046512</t>
+          <t>33.651163</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8851,7 +8851,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x20fed495e61f16b787030a01fda248ac9b1440e2bff075e1455b047031b5be4c</t>
+          <t>0x1e50f9baf79081d66608d3a7ab5b5a987a6af5077945ef59e02797b63779d25e</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>107.79</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785580303</t>
+          <t>1785580305</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>250.674419</t>
+          <t>162.046512</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8963,7 +8963,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x5d4f9ea995b55daae2e64168f1979db64805dfdb2c066be9533eea41e19aa389</t>
+          <t>0x20fed495e61f16b787030a01fda248ac9b1440e2bff075e1455b047031b5be4c</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>107.79</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785580302</t>
+          <t>1785580303</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>49.511628</t>
+          <t>250.674419</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9075,7 +9075,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x58ec131ccccc4609dced3107a7a6729c4349b050ae43bd510e0bf2a0910eeaae</t>
+          <t>0x5d4f9ea995b55daae2e64168f1979db64805dfdb2c066be9533eea41e19aa389</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9083,15 +9083,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>74.15301</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9099,7 +9103,11 @@
           <t>Premier League</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -9152,7 +9160,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785580213</t>
+          <t>1785580302</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9162,7 +9170,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>130.093</t>
+          <t>49.511628</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9179,7 +9187,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xea3905fdcd9b1ad2193748b119a7e458bc170bfb7dcbd3c0a85908ea51ddb63b</t>
+          <t>0x58ec131ccccc4609dced3107a7a6729c4349b050ae43bd510e0bf2a0910eeaae</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9190,7 +9198,7 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>56.39022</t>
+          <t>74.15301</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9226,7 +9234,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+          <t>0x19c474e600655dfbc3f44466abb293af14cd945496e841a711a52e75c96885db</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9256,7 +9264,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785580212</t>
+          <t>1785580213</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9266,7 +9274,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>98.930211</t>
+          <t>130.093</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9283,7 +9291,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x950cdd981b49874d9c07780ab0f05a75c9eaa55c20022cda456f6529599d4534</t>
+          <t>0xea3905fdcd9b1ad2193748b119a7e458bc170bfb7dcbd3c0a85908ea51ddb63b</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9291,54 +9299,46 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>54.58929</t>
+          <t>56.39022</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.4013</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>Rubin Kazan</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Rubin Kazan</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>136.048075</t>
+          <t>98.930211</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9395,31 +9395,39 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x55854836a5bfee9cf8e7d0ab75b0581b46d221967750f4a25ecce99ddf563a3d</t>
+          <t>0x950cdd981b49874d9c07780ab0f05a75c9eaa55c20022cda456f6529599d4534</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>54.58929</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>1.4013</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -9427,27 +9435,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xed1f9246b9fc0972f71238e82ceef603b7365dad40f0d40c40e65009e4d8f1cf</t>
+          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9472,17 +9480,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785579621</t>
+          <t>1785580212</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>7.09217</t>
+          <t>136.048075</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9499,7 +9507,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x3e6fb1125ab2c5cf6dffe098637fd1759f20af5b957a55cc8ac4da659dd9263e</t>
+          <t>0x55854836a5bfee9cf8e7d0ab75b0581b46d221967750f4a25ecce99ddf563a3d</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9576,7 +9584,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785579619</t>
+          <t>1785579621</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9603,18 +9611,18 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x4edfc8afb4d9319e7ca22a617ab98d44d9088cfb97b08b375820e1c2f75a54b7</t>
+          <t>0x3e6fb1125ab2c5cf6dffe098637fd1759f20af5b957a55cc8ac4da659dd9263e</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>26.74218</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9680,7 +9688,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785579591</t>
+          <t>1785579619</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9690,7 +9698,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>37.93217</t>
+          <t>7.09217</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9707,7 +9715,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xdd5efa16642d37a2f2b1a7e3b92e121d783c6088a705f8ed59b37491780656a1</t>
+          <t>0x4edfc8afb4d9319e7ca22a617ab98d44d9088cfb97b08b375820e1c2f75a54b7</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9718,7 +9726,7 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>30.97218</t>
+          <t>26.74218</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9784,7 +9792,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785579590</t>
+          <t>1785579591</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9794,7 +9802,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>43.93217</t>
+          <t>37.93217</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9811,7 +9819,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x71c680237c10938d6ff2f86cc1506136ea79cfb5efe6afba6ae391aeee4bd540</t>
+          <t>0xdd5efa16642d37a2f2b1a7e3b92e121d783c6088a705f8ed59b37491780656a1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9819,19 +9827,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>110.53</t>
+          <t>30.97218</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.705</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9839,11 +9843,7 @@
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -9851,27 +9851,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0xed1f9246b9fc0972f71238e82ceef603b7365dad40f0d40c40e65009e4d8f1cf</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9896,17 +9896,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785578189</t>
+          <t>1785579590</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>245.622222</t>
+          <t>43.93217</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9923,7 +9923,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x9befad38052d4ca6318a4605dbb41c5104b3b7d0effd979d0accdf78a9b920d2</t>
+          <t>0x71c680237c10938d6ff2f86cc1506136ea79cfb5efe6afba6ae391aeee4bd540</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9938,22 +9938,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>110.53</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785578188</t>
+          <t>1785578189</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>194.935252</t>
+          <t>245.622222</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10035,7 +10035,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x3bd55ed63a8eaef652a1be74a03447a94d7f5c35e746d98a3837f7b0fa325a1b</t>
+          <t>0x9befad38052d4ca6318a4605dbb41c5104b3b7d0effd979d0accdf78a9b920d2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10050,22 +10050,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.3475</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xd87e3e74d56c50a95f7eeab8f4e9093ec05b11e3354fb707ffcb563eeb3c5ea4</t>
+          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>175.277778</t>
+          <t>194.935252</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10147,7 +10147,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x19ad74f9aa58d0d1fe6231c86d3c37a94a7ebc8c40fb4bb83351e7bf0c42c216</t>
+          <t>0x3bd55ed63a8eaef652a1be74a03447a94d7f5c35e746d98a3837f7b0fa325a1b</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10162,22 +10162,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
+          <t>0xd87e3e74d56c50a95f7eeab8f4e9093ec05b11e3354fb707ffcb563eeb3c5ea4</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785578187</t>
+          <t>1785578188</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>206.139535</t>
+          <t>175.277778</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10259,12 +10259,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x7d2baf055557c5e62d28cd672a372c6bd91f6bf5dfe4597861420643aeff9dad</t>
+          <t>0x19ad74f9aa58d0d1fe6231c86d3c37a94a7ebc8c40fb4bb83351e7bf0c42c216</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785578167</t>
+          <t>1785578187</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>23.255814</t>
+          <t>206.139535</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10371,7 +10371,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0xe2f3c80f061596dc0f213aaf63fc60ce9d354acd8c210edef40ee8fca220d9d9</t>
+          <t>0x7d2baf055557c5e62d28cd672a372c6bd91f6bf5dfe4597861420643aeff9dad</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785578165</t>
+          <t>1785578167</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10483,12 +10483,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x22d1460f011136dbb3ed1cf16264fc07412888a881d4399ed4e7b633106c77ae</t>
+          <t>0xe2f3c80f061596dc0f213aaf63fc60ce9d354acd8c210edef40ee8fca220d9d9</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785578149</t>
+          <t>1785578165</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>65.162791</t>
+          <t>23.255814</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10595,7 +10595,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xe6d907e5a15573780e8a153c25710ac68b05a2da9c440ce133df93c1b6371fad</t>
+          <t>0x22d1460f011136dbb3ed1cf16264fc07412888a881d4399ed4e7b633106c77ae</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785578147</t>
+          <t>1785578149</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>103.023256</t>
+          <t>65.162791</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10707,7 +10707,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x904a6c948bf4753c9e103e3afc8a7f4fb60c83a95390dade4f5f80838f2a6201</t>
+          <t>0xe6d907e5a15573780e8a153c25710ac68b05a2da9c440ce133df93c1b6371fad</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10715,23 +10715,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>594.4048</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.6625</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -10754,7 +10762,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
+          <t>0xf6ae0846d5f60711ef4f63dc24b64d087fe6927bd4fcdd9aa6000e74be8ee6a9</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10784,7 +10792,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785578076</t>
+          <t>1785578147</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10794,7 +10802,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>897.214792</t>
+          <t>103.023256</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10811,7 +10819,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0xeaa0f12279579996121f820f6e7c355f29cc7a7c0aff9e0d45b192a79bb86d53</t>
+          <t>0x904a6c948bf4753c9e103e3afc8a7f4fb60c83a95390dade4f5f80838f2a6201</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10822,17 +10830,17 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>422.63563</t>
+          <t>594.4048</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.6625</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -10858,7 +10866,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
+          <t>0x91d3336533922b667aa05ca59acbba9e0e3076eae36486cdeaa9f496e626126f</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10888,7 +10896,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785578075</t>
+          <t>1785578076</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10898,7 +10906,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>753.025621</t>
+          <t>897.214792</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10915,39 +10923,31 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0xe0818cb9f098e011b143578453eadde11363dedcc95f61e9dfca94267932d2cf</t>
+          <t>0xeaa0f12279579996121f820f6e7c355f29cc7a7c0aff9e0d45b192a79bb86d53</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>422.63563</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>CSKA Moscow -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
+          <t>0x7311cae38fff479fa25f8ecb5325c65467e86bfb8f876fcf88767f9ce2143b80</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785572887</t>
+          <t>1785578075</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>20.464286</t>
+          <t>753.025621</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -11027,12 +11027,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0xdae6a6bc9c468e345de6b0edd818d404c5d319a8b35d8b8e089f27c055c389b5</t>
+          <t>0xe0818cb9f098e011b143578453eadde11363dedcc95f61e9dfca94267932d2cf</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -11042,22 +11042,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>108.62998</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>CSKA Moscow -1</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0x250c9978ebf5b011075be1d4db3f8d11c84ae4775b2a15381141c2041819671d</t>
+          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1785572661</t>
+          <t>1785572887</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>136.213141</t>
+          <t>20.464286</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11139,31 +11139,39 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0x8287809c6ecbf4350c5b00a693999a7413ec85bf151e6bc30a165f00a63e0841</t>
+          <t>0xdae6a6bc9c468e345de6b0edd818d404c5d319a8b35d8b8e089f27c055c389b5</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>11.39998</t>
+          <t>108.62998</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -11171,27 +11179,27 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0xd2c373d98f28160b1937cb16fc225505947dd2558aed807adb6793d0ba065168</t>
+          <t>0x250c9978ebf5b011075be1d4db3f8d11c84ae4775b2a15381141c2041819671d</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -11216,17 +11224,17 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1785572520</t>
+          <t>1785572661</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>15.971951</t>
+          <t>136.213141</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11243,28 +11251,28 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0x3b18e7fae3a0845fdb30a3cbe728a545cae4e662d0b4f73499445c8c15b3fc40</t>
+          <t>0x8287809c6ecbf4350c5b00a693999a7413ec85bf151e6bc30a165f00a63e0841</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11.39998</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -11275,27 +11283,27 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+          <t>0xd2c373d98f28160b1937cb16fc225505947dd2558aed807adb6793d0ba065168</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -11320,17 +11328,17 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1785571166</t>
+          <t>1785572520</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>29.411765</t>
+          <t>15.971951</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11347,28 +11355,28 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0x74da0033cbaaf0989652d45e0a379a053226dca51e774fe8f3d59364a7ed7bc3</t>
+          <t>0x3b18e7fae3a0845fdb30a3cbe728a545cae4e662d0b4f73499445c8c15b3fc40</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>21.9974</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -11394,7 +11402,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -11424,7 +11432,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1785571136</t>
+          <t>1785571166</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11434,7 +11442,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>29.477253</t>
+          <t>29.411765</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11451,7 +11459,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0xdf6e0cf8b56844dd97ec7cd857e88927c45b93f08b350ac9344b7a0606e045b8</t>
+          <t>0x74da0033cbaaf0989652d45e0a379a053226dca51e774fe8f3d59364a7ed7bc3</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11462,7 +11470,7 @@
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>52.31835</t>
+          <t>21.9974</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -11528,7 +11536,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1785571135</t>
+          <t>1785571136</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11538,7 +11546,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>70.108342</t>
+          <t>29.477253</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11555,7 +11563,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0x018d60ff481049c67bba92e9b54e0d55c42b86a5d701c0b1c584e9807ee17e54</t>
+          <t>0xdf6e0cf8b56844dd97ec7cd857e88927c45b93f08b350ac9344b7a0606e045b8</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11566,17 +11574,17 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>14.89036</t>
+          <t>52.31835</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -11602,7 +11610,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -11642,7 +11650,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>87.590353</t>
+          <t>70.108342</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11659,7 +11667,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0xa5cc97a62584698f6c4048c5f24e84a8eadf70fd65b8935042102ef7c64fb9d8</t>
+          <t>0x018d60ff481049c67bba92e9b54e0d55c42b86a5d701c0b1c584e9807ee17e54</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11670,17 +11678,17 @@
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>33.69787</t>
+          <t>14.89036</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1.5762</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -11691,27 +11699,27 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>0xeb29ac30b54329d5d60f9106332c47c7d06e00b17061f03af8f7e4b413a058ba</t>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -11736,17 +11744,17 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>1785571067</t>
+          <t>1785571135</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>58.477866</t>
+          <t>87.590353</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11763,39 +11771,31 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0xf321b64477a115c8937a87a1a8313c82a213b8e568c8f88293a4375fba41be54</t>
+          <t>0xa5cc97a62584698f6c4048c5f24e84a8eadf70fd65b8935042102ef7c64fb9d8</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>33.69787</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.5762</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Lokomotiv Moscow</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -11803,27 +11803,27 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>0x3890375e41e397b7fd55fb869bda99e7fceb1ca0319fe030519bd2ec2cf5bc31</t>
+          <t>0xeb29ac30b54329d5d60f9106332c47c7d06e00b17061f03af8f7e4b413a058ba</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -11848,17 +11848,17 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>1785567916</t>
+          <t>1785571067</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>2.233062</t>
+          <t>58.477866</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11875,31 +11875,39 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0xe3ddd7c883204ad1dba275364ab1e46eb717f308b3dedc5acbd7703d980bec00</t>
+          <t>0xf321b64477a115c8937a87a1a8313c82a213b8e568c8f88293a4375fba41be54</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moscow</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -11907,27 +11915,27 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
+          <t>0x3890375e41e397b7fd55fb869bda99e7fceb1ca0319fe030519bd2ec2cf5bc31</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -11952,17 +11960,17 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>1785563385</t>
+          <t>1785567916</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>6.700141</t>
+          <t>2.233062</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -11979,23 +11987,23 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0xa4c6ae8963dfa3b202fe6ce8ce74f74e1dbf632ba3fc5ac6cee71b986816c930</t>
+          <t>0xe3ddd7c883204ad1dba275364ab1e46eb717f308b3dedc5acbd7703d980bec00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>77.76784</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -12056,7 +12064,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>1785563353</t>
+          <t>1785563385</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -12066,7 +12074,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>104.737832</t>
+          <t>6.700141</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -12083,28 +12091,28 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0x841657eb70bcebb4ab52934f0882d697225406f5e7fd8417bc066ef32cfd9f3f</t>
+          <t>0xa4c6ae8963dfa3b202fe6ce8ce74f74e1dbf632ba3fc5ac6cee71b986816c930</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>77.76784</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -12130,7 +12138,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+          <t>0x2f6d958c1453ad464ccaac2f982b695c48103adb49e4a82b0a095141ba5d4651</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -12160,7 +12168,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>1785563065</t>
+          <t>1785563353</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -12170,7 +12178,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>104.737832</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12187,7 +12195,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0xf274d715150d62a93d353cede0f6ff9c88848ac391602271e47187d10e35b365</t>
+          <t>0x841657eb70bcebb4ab52934f0882d697225406f5e7fd8417bc066ef32cfd9f3f</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12198,7 +12206,7 @@
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -12264,7 +12272,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>1785563064</t>
+          <t>1785563065</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -12274,7 +12282,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>2.909091</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -12291,7 +12299,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0xf8e15936a562a6c53c3f0b156df3f4beef97db21efe52a96112e59b7b71d2cfc</t>
+          <t>0xf274d715150d62a93d353cede0f6ff9c88848ac391602271e47187d10e35b365</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12302,7 +12310,7 @@
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -12368,7 +12376,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>1785562017</t>
+          <t>1785563064</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -12378,7 +12386,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>133.527273</t>
+          <t>2.909091</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -12395,7 +12403,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0x31383c91bcc01015e13e5fd2b9bea5aca6c5af939719601af5d89e0d14f917d1</t>
+          <t>0xf8e15936a562a6c53c3f0b156df3f4beef97db21efe52a96112e59b7b71d2cfc</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12406,17 +12414,17 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -12442,7 +12450,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -12472,7 +12480,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>1785561847</t>
+          <t>1785562017</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -12482,7 +12490,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>133.527273</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12499,7 +12507,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0x62d0c1650da9a9f20785ab148cd57757523f593981c50f9121d975d5671dc22c</t>
+          <t>0x31383c91bcc01015e13e5fd2b9bea5aca6c5af939719601af5d89e0d14f917d1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12510,17 +12518,17 @@
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -12546,7 +12554,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
+          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -12576,7 +12584,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1785561830</t>
+          <t>1785561847</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -12586,7 +12594,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>34.376812</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -12603,28 +12611,28 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0xca8103b7c29655e3359ce0c76ab74b1e550d22a25b2697a62f009036198b340d</t>
+          <t>0x62d0c1650da9a9f20785ab148cd57757523f593981c50f9121d975d5671dc22c</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -12650,7 +12658,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
+          <t>0xe035c7d26a63c51c5816fde63ba1d15007db8b7e6fc8337b56e366fa26a24231</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -12680,7 +12688,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>1785561684</t>
+          <t>1785561830</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -12690,7 +12698,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>29.411765</t>
+          <t>34.376812</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -12707,18 +12715,18 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0xd2b6ca67a5a2d819fc0cf69e7b7cb17aef0d37ea042ab1d803ea19a79869cf1c</t>
+          <t>0xca8103b7c29655e3359ce0c76ab74b1e550d22a25b2697a62f009036198b340d</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>15.91241</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -12784,7 +12792,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>1785561659</t>
+          <t>1785561684</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -12794,7 +12802,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>93.602412</t>
+          <t>29.411765</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -12811,28 +12819,28 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0x9df3204fd72e0052ebf44ed8084dee18335fa60165de967589f7ffece734f21d</t>
+          <t>0xd2b6ca67a5a2d819fc0cf69e7b7cb17aef0d37ea042ab1d803ea19a79869cf1c</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0x8AaDb828882f34790D0C35aE0534a6BbDDA6ad19</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15.91241</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -12858,7 +12866,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
+          <t>0x07bb32649e8841f9afdcd2cd1c708b25963cb3b191657b4eb8f21a6699a031dc</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -12888,7 +12896,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>1785561561</t>
+          <t>1785561659</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12898,7 +12906,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>21.621622</t>
+          <t>93.602412</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -12915,28 +12923,28 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0x1c651915969f4f1991cb4f8083b94c18de450a29ab1d239f29fd2136f09013cd</t>
+          <t>0x9df3204fd72e0052ebf44ed8084dee18335fa60165de967589f7ffece734f21d</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8AaDb828882f34790D0C35aE0534a6BbDDA6ad19</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>39.53998</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -12947,27 +12955,27 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>CSKA Moscow</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Krylia Sovetov</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
+          <t>0x963410ef2900ff4627c5c3a780f21fef042081dbdb2b4a1dc616bac8a42e56fb</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536033</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12992,17 +13000,17 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>1785559258</t>
+          <t>1785561561</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785590100</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>55.39752</t>
+          <t>21.621622</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -13019,7 +13027,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0xfe4e061b2e2e2540fd50c22f993ed8e84c7d22f3208b337d5a326d6444353f09</t>
+          <t>0x1c651915969f4f1991cb4f8083b94c18de450a29ab1d239f29fd2136f09013cd</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13030,17 +13038,17 @@
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>97.43997</t>
+          <t>39.53998</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -13066,7 +13074,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>0x5b5b30e2f6739fc9828801a4bc6c1fd66d2d048516210562005b195dab2ed7e8</t>
+          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -13096,7 +13104,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>1785559257</t>
+          <t>1785559258</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -13106,7 +13114,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>124.325321</t>
+          <t>55.39752</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -13123,7 +13131,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0x08024130d9cb2665d1fada581c354f0d9912d9be188b8a5b5cd319c76fc8f84b</t>
+          <t>0xfe4e061b2e2e2540fd50c22f993ed8e84c7d22f3208b337d5a326d6444353f09</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13134,17 +13142,17 @@
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0.00083</t>
+          <t>97.43997</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -13170,7 +13178,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
+          <t>0x5b5b30e2f6739fc9828801a4bc6c1fd66d2d048516210562005b195dab2ed7e8</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -13210,7 +13218,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>0.001163</t>
+          <t>124.325321</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -13227,27 +13235,23 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0x7a11de4f80dc40500c7c27e609aa7ce468977e4b318ea22ee056badb255acac0</t>
+          <t>0x08024130d9cb2665d1fada581c354f0d9912d9be188b8a5b5cd319c76fc8f84b</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>0.00083</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1.2775</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13255,11 +13259,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Dynamo Dagestan Makhachkala</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -13267,27 +13267,27 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
+          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -13312,17 +13312,17 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>1785554288</t>
+          <t>1785559257</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>83.063063</t>
+          <t>0.001163</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -13339,12 +13339,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0x13a6ce7009e637abe73138bc7868471610982f652ed68f38fbb93a4e68405e6c</t>
+          <t>0x7a11de4f80dc40500c7c27e609aa7ce468977e4b318ea22ee056badb255acac0</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>1785552612</t>
+          <t>1785554288</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>18.018018</t>
+          <t>83.063063</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -13451,12 +13451,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0x17588dd455f17e31e06c55e5d5c91052a57c1fc2c2711a0891e74386a507ec57</t>
+          <t>0x13a6ce7009e637abe73138bc7868471610982f652ed68f38fbb93a4e68405e6c</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>1785552583</t>
+          <t>1785552612</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>52.612613</t>
+          <t>18.018018</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -13563,23 +13563,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0x7e4e77fa047e471fb7a25555ab8b596db1c260554e819bf1e556c3fb95efcdad</t>
+          <t>0x17588dd455f17e31e06c55e5d5c91052a57c1fc2c2711a0891e74386a507ec57</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>63.81998</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1.7125</t>
+          <t>1.2775</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -13587,7 +13591,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Dynamo Dagestan Makhachkala</t>
+        </is>
+      </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -13595,27 +13603,27 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
+          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -13640,17 +13648,17 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>1785550426</t>
+          <t>1785552583</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>89.571902</t>
+          <t>52.612613</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -13667,27 +13675,23 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0xe168538382bb9379f973bea17e97bdbec6d33bf8f1675b71dfc9f45ecde2301e</t>
+          <t>0x7e4e77fa047e471fb7a25555ab8b596db1c260554e819bf1e556c3fb95efcdad</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>63.81998</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1.2775</t>
+          <t>1.7125</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -13695,11 +13699,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Dynamo Dagestan Makhachkala</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -13707,27 +13707,27 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Dynamo Dagestan Makhachkala</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Lokomotiv Moscow</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
+          <t>0x3bd78aefd9b4cfcf06d7e7a59d0f234774a8b0a27a77b1eb2b706312bd1e518c</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>L19536924</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -13752,17 +13752,17 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>1785549278</t>
+          <t>1785550426</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>1785598200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>18.018018</t>
+          <t>89.571902</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -13779,12 +13779,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0x01f52f51af10033e9f1c42cddafc3bf0296939cdfd57ee81fc03f9b4ce79db99</t>
+          <t>0xe168538382bb9379f973bea17e97bdbec6d33bf8f1675b71dfc9f45ecde2301e</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>1785549255</t>
+          <t>1785549278</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>57.405405</t>
+          <t>18.018018</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -13891,7 +13891,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0x1638d462ac081048e75f74389a4ff26e18b1ae1b526d3aeb9de1440589cd1e5d</t>
+          <t>0x01f52f51af10033e9f1c42cddafc3bf0296939cdfd57ee81fc03f9b4ce79db99</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13906,22 +13906,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>242.37998</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.2775</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -13931,27 +13931,27 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
+          <t>Dynamo Dagestan Makhachkala vs Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>FC Baltika Kaliningrad</t>
+          <t>Dynamo Dagestan Makhachkala</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Dynamo Moscow</t>
+          <t>Lokomotiv Moscow</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
+          <t>0x0b47f6a4d9e5ca93e4d828e0c9eccaeb566e5dc29d7abf8b0c08971b1926d853</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>L19536935</t>
+          <t>L19536924</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -13976,17 +13976,17 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>1785522300</t>
+          <t>1785549255</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>1785606300</t>
+          <t>1785598200</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>336.638861</t>
+          <t>57.405405</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -14003,12 +14003,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0xbb7e9ff01a18bfc8edad554bb31f15afc9af81a591df798303c216a31f4f60a2</t>
+          <t>0x1638d462ac081048e75f74389a4ff26e18b1ae1b526d3aeb9de1440589cd1e5d</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14018,22 +14018,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>42.87</t>
+          <t>242.37998</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1.3912</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -14043,27 +14043,27 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>FC Baltika Kaliningrad vs Dynamo Moscow</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>FC Baltika Kaliningrad</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Dynamo Moscow</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
+          <t>0x26403f62452b8203773eb30822eb65b7eef914faa7331c0c36b66562b6169a51</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536935</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -14088,17 +14088,17 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>1785519268</t>
+          <t>1785522300</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785606300</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>109.571885</t>
+          <t>336.638861</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -14115,7 +14115,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0xb20c524d4e546a7083e83d50954cb82e74d2f35919a693305ef85bcd1297f018</t>
+          <t>0xbb7e9ff01a18bfc8edad554bb31f15afc9af81a591df798303c216a31f4f60a2</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -14123,15 +14123,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>6.81967</t>
+          <t>42.87</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.3912</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14139,7 +14143,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -14162,7 +14170,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+          <t>0x07722bc1915f9c62672c1463f51f0999a3f9d64954cbe614ec3ca28cd49c5ec3</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -14202,7 +14210,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>9.99219</t>
+          <t>109.571885</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -14219,7 +14227,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0x4f0a3bc80edb843b0944d88bf4e31147f77d117de6bec90e861ee3f30e05ab04</t>
+          <t>0xb20c524d4e546a7083e83d50954cb82e74d2f35919a693305ef85bcd1297f018</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -14230,17 +14238,17 @@
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>6.81967</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1.5488</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -14266,7 +14274,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
+          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -14296,7 +14304,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>1785519266</t>
+          <t>1785519268</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -14306,7 +14314,7 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>25.18451</t>
+          <t>9.99219</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -14323,18 +14331,18 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0x5ba31b6e54e59ca06de6605e21a3984e6bef3be97c4a38cb1fef0f420c3c5762</t>
+          <t>0x4f0a3bc80edb843b0944d88bf4e31147f77d117de6bec90e861ee3f30e05ab04</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -14400,7 +14408,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>1785517580</t>
+          <t>1785519266</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -14410,7 +14418,7 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>9.111617</t>
+          <t>25.18451</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -14427,18 +14435,18 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0x34ae51184c54f771408cd03c9262de0e4ea1554f41b9cf4d3f7f2c5d4d746850</t>
+          <t>0x5ba31b6e54e59ca06de6605e21a3984e6bef3be97c4a38cb1fef0f420c3c5762</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>13.93611</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -14504,7 +14512,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>1785517575</t>
+          <t>1785517580</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -14514,7 +14522,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>25.3961</t>
+          <t>9.111617</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -14531,28 +14539,28 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0x7029f30f1995c9929d909d63df9f8e25356451c2543674cd96d9a354775d1cd1</t>
+          <t>0x34ae51184c54f771408cd03c9262de0e4ea1554f41b9cf4d3f7f2c5d4d746850</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>13.93611</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.5488</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -14563,27 +14571,27 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Rodina Moskva vs Rostov FK</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Rostov FK</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>0x79bda80ec32380a53cc33c980754cff46b3880a7317dd6e783f523b986aea91a</t>
+          <t>0x3f4415a2a8982e4ee555d5a13d058ac4f70817d9e75f9a3b633aac5216997222</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>L19536024</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -14608,17 +14616,17 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>1785513066</t>
+          <t>1785517575</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>1.405961</t>
+          <t>25.3961</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -14635,27 +14643,23 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0xa0c8d19ccd8222fe5808f3173eb4463c8de341ddcfcb086f400632089e4f0be4</t>
+          <t>0x7029f30f1995c9929d909d63df9f8e25356451c2543674cd96d9a354775d1cd1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>50.36</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1.3375</t>
+          <t>1.7113</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -14663,11 +14667,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Akron Tolyatti</t>
-        </is>
-      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -14675,27 +14675,27 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Rubin Kazan</t>
+          <t>Rodina Moskva vs Rostov FK</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Akron Tolyatti</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Rostov FK</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
+          <t>0x79bda80ec32380a53cc33c980754cff46b3880a7317dd6e783f523b986aea91a</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>L19536035</t>
+          <t>L19536024</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -14720,17 +14720,17 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>1785497556</t>
+          <t>1785513066</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>1785582000</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>149.214815</t>
+          <t>1.405961</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -14747,12 +14747,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0x284f0b4a1de283358a3577badffac14ecc5afcfdc28ce21985a9cb86481ba6cc</t>
+          <t>0xa0c8d19ccd8222fe5808f3173eb4463c8de341ddcfcb086f400632089e4f0be4</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0x6d158A0b6c9Df0483460f6a656673630210CAA4a</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50.36</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.3375</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -14787,27 +14787,27 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Rodina Moskva vs Rostov FK</t>
+          <t>Akron Tolyatti vs Rubin Kazan</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Akron Tolyatti</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Rostov FK</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>0xc2ed80c842ab0c1d24361f465ff9c0b8137d5178739873b6e3325008d77dd204</t>
+          <t>0x978d74fa55b35c6a31af5bda64d8c105c1646284a80d5450780fb263788792ba</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>L19536024</t>
+          <t>L19536035</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -14832,17 +14832,17 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>1785497412</t>
+          <t>1785497556</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>1785517200</t>
+          <t>1785582000</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>224.089636</t>
+          <t>149.214815</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -14859,31 +14859,39 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0x82023bc913cac320bbcec8856b93c61ced3824bae2ff614f7aeb447196f63721</t>
+          <t>0x284f0b4a1de283358a3577badffac14ecc5afcfdc28ce21985a9cb86481ba6cc</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>0x6d158A0b6c9Df0483460f6a656673630210CAA4a</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>139.07045</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1.7913</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Premier League</t>
@@ -14891,27 +14899,27 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>CSKA Moscow vs Krylia Sovetov</t>
+          <t>Rodina Moskva vs Rostov FK</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Rostov FK</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+          <t>0xc2ed80c842ab0c1d24361f465ff9c0b8137d5178739873b6e3325008d77dd204</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>L19536033</t>
+          <t>L19536024</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -14936,17 +14944,17 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>1785492025</t>
+          <t>1785497412</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>1785590100</t>
+          <t>1785517200</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>175.760442</t>
+          <t>224.089636</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -14963,7 +14971,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0xb79b0374865c7617b60514b2180feb26aead2aaca0895843000b71787d8212f5</t>
+          <t>0x82023bc913cac320bbcec8856b93c61ced3824bae2ff614f7aeb447196f63721</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14974,7 +14982,7 @@
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>38.81386</t>
+          <t>139.07045</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -15040,7 +15048,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>1785492024</t>
+          <t>1785492025</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -15050,7 +15058,7 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>49.053852</t>
+          <t>175.760442</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
@@ -15067,110 +15075,214 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>0xb79b0374865c7617b60514b2180feb26aead2aaca0895843000b71787d8212f5</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>38.81386</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1.7913</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>0x25dea896106f6d0a84bac4d64a12e8dc4788c5bb617516256ef26de81fa0a8f2</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>L19536033</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>1785492024</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>1785590100</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>49.053852</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
           <t>0x35c722e47edc576e91fff2a56006e70c47630baaf10fd0a9c8c7187b33e14e24</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
         <is>
           <t>1.3113</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny vs Spartak Moskva</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t>FC Akhmat Grozny</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>Spartak Moskva</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t>0xba2ac566f21d9b66fba41da0a24a5d93737f4a0c2789de13002227a82662899c</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t>L19537277</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr">
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
         <is>
           <t>1785344429</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
+      <c r="S137" t="inlineStr">
         <is>
           <t>1785691800</t>
         </is>
       </c>
-      <c r="T136" t="inlineStr">
+      <c r="T137" t="inlineStr">
         <is>
           <t>3.212851</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="U137" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr">
+      <c r="V137" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
